--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.875</v>
+        <v>34.75</v>
       </c>
       <c r="H253" t="n">
-        <v>118.865</v>
+        <v>118.439</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.404999</v>
+        <v>47.485001</v>
       </c>
       <c r="H504" t="n">
-        <v>136.28</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.012405</v>
+        <v>64.012398</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.43092300000001</v>
+        <v>64.430908</v>
       </c>
       <c r="H507" t="n">
         <v>100.6538</v>
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.32384500000001</v>
+        <v>64.323853</v>
       </c>
       <c r="H510" t="n">
-        <v>100.4865</v>
+        <v>100.4866</v>
       </c>
     </row>
     <row r="511">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.97595200000001</v>
+        <v>64.975945</v>
       </c>
       <c r="H512" t="n">
         <v>101.5053</v>
@@ -20177,7 +20177,7 @@
         <v>64.868858</v>
       </c>
       <c r="H520" t="n">
-        <v>101.3379</v>
+        <v>101.338</v>
       </c>
     </row>
     <row r="521">
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H523" t="n">
         <v>101.7051</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H527" t="n">
         <v>102.363</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H531" t="n">
         <v>103.7093</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.564171</v>
+        <v>65.56416299999999</v>
       </c>
       <c r="H534" t="n">
         <v>102.4242</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H535" t="n">
         <v>102.2865</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H537" t="n">
         <v>102.9902</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H538" t="n">
         <v>102.3018</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H539" t="n">
         <v>103.4339</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H540" t="n">
         <v>103.7093</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.308426</v>
+        <v>66.308441</v>
       </c>
       <c r="H541" t="n">
-        <v>103.5868</v>
+        <v>103.5869</v>
       </c>
     </row>
     <row r="542">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H543" t="n">
         <v>104.3212</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H544" t="n">
         <v>104.2141</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H546" t="n">
         <v>104.3212</v>
@@ -21355,7 +21355,7 @@
         <v>66.357399</v>
       </c>
       <c r="H551" t="n">
-        <v>103.6633</v>
+        <v>103.6634</v>
       </c>
     </row>
     <row r="552">
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H555" t="n">
         <v>106.1417</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H557" t="n">
         <v>104.9025</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H558" t="n">
         <v>104.3365</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H561" t="n">
-        <v>103.7245</v>
+        <v>103.7246</v>
       </c>
     </row>
     <row r="562">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H562" t="n">
         <v>103.5104</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H563" t="n">
         <v>103.8775</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H564" t="n">
         <v>104.2906</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H565" t="n">
         <v>105.2544</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.6369</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H569" t="n">
         <v>105.0555</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H571" t="n">
         <v>105.8357</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H572" t="n">
         <v>106.0652</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H573" t="n">
         <v>105.6981</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H575" t="n">
         <v>105.6063</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.85573599999999</v>
+        <v>67.855728</v>
       </c>
       <c r="H576" t="n">
         <v>106.004</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H577" t="n">
         <v>105.8663</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H578" t="n">
         <v>106.463</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H579" t="n">
         <v>105.5145</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H580" t="n">
         <v>105.6216</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H581" t="n">
         <v>106.2251</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H582" t="n">
         <v>106.6559</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H587" t="n">
         <v>107.6406</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H588" t="n">
         <v>108.7791</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H594" t="n">
         <v>110.3947</v>
@@ -23065,7 +23065,7 @@
         <v>71.739822</v>
       </c>
       <c r="H596" t="n">
-        <v>112.0717</v>
+        <v>112.0718</v>
       </c>
     </row>
     <row r="597">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H597" t="n">
         <v>111.9948</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H599" t="n">
         <v>110.0716</v>
@@ -23217,7 +23217,7 @@
         <v>70.76477800000001</v>
       </c>
       <c r="H600" t="n">
-        <v>110.5485</v>
+        <v>110.5486</v>
       </c>
     </row>
     <row r="601">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H604" t="n">
         <v>110.6101</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H608" t="n">
         <v>112.6103</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H610" t="n">
         <v>114.4874</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H611" t="n">
         <v>113.6565</v>
@@ -23708,10 +23708,10 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H613" t="n">
-        <v>115.1643</v>
+        <v>115.1644</v>
       </c>
     </row>
     <row r="614">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H615" t="n">
         <v>116.4414</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H617" t="n">
         <v>115.9798</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H618" t="n">
         <v>116.0721</v>
@@ -23939,7 +23939,7 @@
         <v>74.28085299999999</v>
       </c>
       <c r="H619" t="n">
-        <v>116.0413</v>
+        <v>116.0414</v>
       </c>
     </row>
     <row r="620">
@@ -23977,7 +23977,7 @@
         <v>74.911186</v>
       </c>
       <c r="H620" t="n">
-        <v>117.026</v>
+        <v>117.0261</v>
       </c>
     </row>
     <row r="621">
@@ -24015,7 +24015,7 @@
         <v>74.911186</v>
       </c>
       <c r="H621" t="n">
-        <v>117.026</v>
+        <v>117.0261</v>
       </c>
     </row>
     <row r="622">
@@ -24202,10 +24202,10 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H626" t="n">
-        <v>118.2569</v>
+        <v>118.257</v>
       </c>
     </row>
     <row r="627">
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H629" t="n">
         <v>115.2413</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H634" t="n">
         <v>114.2412</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H635" t="n">
         <v>113.795</v>
@@ -25307,7 +25307,7 @@
         <v>73.903564</v>
       </c>
       <c r="H655" t="n">
-        <v>115.4519</v>
+        <v>115.452</v>
       </c>
     </row>
     <row r="656">
@@ -25725,7 +25725,7 @@
         <v>74.200523</v>
       </c>
       <c r="H666" t="n">
-        <v>115.9158</v>
+        <v>115.9159</v>
       </c>
     </row>
     <row r="667">
@@ -26105,7 +26105,7 @@
         <v>75.42795599999999</v>
       </c>
       <c r="H676" t="n">
-        <v>117.8333</v>
+        <v>117.8334</v>
       </c>
     </row>
     <row r="677">
@@ -26637,7 +26637,7 @@
         <v>77.199821</v>
       </c>
       <c r="H690" t="n">
-        <v>120.6013</v>
+        <v>120.6014</v>
       </c>
     </row>
     <row r="691">
@@ -27131,7 +27131,7 @@
         <v>78.349998</v>
       </c>
       <c r="H703" t="n">
-        <v>122.3981</v>
+        <v>122.3982</v>
       </c>
     </row>
     <row r="704">
@@ -27169,7 +27169,7 @@
         <v>78.980003</v>
       </c>
       <c r="H704" t="n">
-        <v>123.3823</v>
+        <v>123.3824</v>
       </c>
     </row>
     <row r="705">
@@ -27207,7 +27207,7 @@
         <v>78.620003</v>
       </c>
       <c r="H705" t="n">
-        <v>122.8199</v>
+        <v>122.82</v>
       </c>
     </row>
     <row r="706">
@@ -27283,7 +27283,7 @@
         <v>79.120003</v>
       </c>
       <c r="H707" t="n">
-        <v>123.601</v>
+        <v>123.6011</v>
       </c>
     </row>
     <row r="708">
@@ -27435,7 +27435,7 @@
         <v>78.889999</v>
       </c>
       <c r="H711" t="n">
-        <v>123.2417</v>
+        <v>123.2418</v>
       </c>
     </row>
     <row r="712">
@@ -27587,7 +27587,7 @@
         <v>79.980003</v>
       </c>
       <c r="H715" t="n">
-        <v>124.9445</v>
+        <v>124.9446</v>
       </c>
     </row>
     <row r="716">
@@ -27701,7 +27701,7 @@
         <v>79.849998</v>
       </c>
       <c r="H718" t="n">
-        <v>124.7414</v>
+        <v>124.7415</v>
       </c>
     </row>
     <row r="719">
@@ -28119,7 +28119,7 @@
         <v>81.16999800000001</v>
       </c>
       <c r="H729" t="n">
-        <v>126.8035</v>
+        <v>126.8036</v>
       </c>
     </row>
     <row r="730">
@@ -28613,7 +28613,7 @@
         <v>81.94000200000001</v>
       </c>
       <c r="H742" t="n">
-        <v>128.0064</v>
+        <v>128.0065</v>
       </c>
     </row>
     <row r="743">
@@ -28689,7 +28689,7 @@
         <v>81.620003</v>
       </c>
       <c r="H744" t="n">
-        <v>127.5065</v>
+        <v>127.5066</v>
       </c>
     </row>
     <row r="745">
@@ -28727,7 +28727,7 @@
         <v>81.300003</v>
       </c>
       <c r="H745" t="n">
-        <v>127.0066</v>
+        <v>127.0067</v>
       </c>
     </row>
     <row r="746">
@@ -29031,7 +29031,7 @@
         <v>81.66999800000001</v>
       </c>
       <c r="H753" t="n">
-        <v>127.5846</v>
+        <v>127.5847</v>
       </c>
     </row>
     <row r="754">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.529999</v>
+        <v>81.760002</v>
       </c>
       <c r="H755" t="n">
-        <v>127.3659</v>
+        <v>127.7253</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.410004</v>
+        <v>126.82</v>
       </c>
       <c r="H1006" t="n">
-        <v>121.888</v>
+        <v>122.2833</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.410004</v>
+        <v>126.82</v>
       </c>
       <c r="H1257" t="n">
-        <v>121.888</v>
+        <v>122.2833</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.410004</v>
+        <v>126.82</v>
       </c>
       <c r="H1508" t="n">
-        <v>121.888</v>
+        <v>122.2833</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.551022</v>
+        <v>53.551018</v>
       </c>
       <c r="H1511" t="n">
         <v>101.3078</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1516" t="n">
         <v>102.3209</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>64.589996</v>
+        <v>64.529999</v>
       </c>
       <c r="H1760" t="n">
-        <v>122.1913</v>
+        <v>122.0778</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.294998</v>
+        <v>34.084999</v>
       </c>
       <c r="H253" t="n">
-        <v>113.6537</v>
+        <v>112.9577</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.380001</v>
+        <v>48.415001</v>
       </c>
       <c r="H504" t="n">
-        <v>136.8987</v>
+        <v>136.9977</v>
       </c>
     </row>
     <row r="505">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.489311</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H512" t="n">
         <v>100.6838</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H514" t="n">
         <v>101.1235</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.810112</v>
+        <v>64.810104</v>
       </c>
       <c r="H518" t="n">
         <v>101.1846</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H521" t="n">
         <v>101.521</v>
@@ -20288,10 +20288,10 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H523" t="n">
-        <v>102.3008</v>
+        <v>102.3007</v>
       </c>
     </row>
     <row r="524">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H527" t="n">
         <v>103.6462</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.56416299999999</v>
+        <v>65.564171</v>
       </c>
       <c r="H530" t="n">
         <v>102.3619</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H536" t="n">
         <v>103.6462</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308426</v>
       </c>
       <c r="H537" t="n">
         <v>103.5239</v>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H540" t="n">
-        <v>104.1507</v>
+        <v>104.1508</v>
       </c>
     </row>
     <row r="541">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H541" t="n">
         <v>103.952</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.2272</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H563" t="n">
         <v>105.5727</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.659874</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.6338</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H570" t="n">
         <v>105.6491</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.855728</v>
+        <v>67.85573599999999</v>
       </c>
       <c r="H572" t="n">
         <v>105.9396</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H573" t="n">
         <v>105.802</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H575" t="n">
         <v>105.4503</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.900002</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H755" t="n">
-        <v>127.8662</v>
+        <v>127.7413</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.410004</v>
+        <v>127.330002</v>
       </c>
       <c r="H1006" t="n">
-        <v>121.1237</v>
+        <v>121.0476</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.410004</v>
+        <v>127.330002</v>
       </c>
       <c r="H1257" t="n">
-        <v>121.1237</v>
+        <v>121.0476</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.410004</v>
+        <v>127.330002</v>
       </c>
       <c r="H1508" t="n">
-        <v>121.1237</v>
+        <v>121.0476</v>
       </c>
     </row>
     <row r="1509">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>64.93000000000001</v>
+        <v>64.970001</v>
       </c>
       <c r="H1760" t="n">
-        <v>120.7877</v>
+        <v>120.8621</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.323853</v>
+        <v>64.32384500000001</v>
       </c>
       <c r="H506" t="n">
         <v>100.4255</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.41145299999999</v>
+        <v>64.411446</v>
       </c>
       <c r="H507" t="n">
         <v>100.5622</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H512" t="n">
         <v>100.6838</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H515" t="n">
         <v>101.0164</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H518" t="n">
         <v>101.1846</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H527" t="n">
         <v>103.6462</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H529" t="n">
         <v>101.8421</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.564171</v>
+        <v>65.56416299999999</v>
       </c>
       <c r="H530" t="n">
         <v>102.3619</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H534" t="n">
         <v>102.2396</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H536" t="n">
         <v>103.6462</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.308426</v>
+        <v>66.308441</v>
       </c>
       <c r="H537" t="n">
         <v>103.5239</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H539" t="n">
         <v>104.2578</v>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H540" t="n">
-        <v>104.1508</v>
+        <v>104.1507</v>
       </c>
     </row>
     <row r="541">
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H542" t="n">
         <v>104.2578</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H549" t="n">
         <v>104.1966</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H554" t="n">
         <v>104.2731</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H555" t="n">
         <v>103.2334</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H558" t="n">
         <v>103.4474</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H559" t="n">
         <v>103.8144</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H561" t="n">
         <v>105.1904</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H563" t="n">
         <v>105.5727</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H565" t="n">
         <v>104.9917</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H569" t="n">
         <v>105.6338</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H571" t="n">
         <v>105.5421</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.85573599999999</v>
+        <v>67.855728</v>
       </c>
       <c r="H572" t="n">
         <v>105.9396</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H573" t="n">
         <v>105.802</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H574" t="n">
         <v>106.3983</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H576" t="n">
         <v>105.5574</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H577" t="n">
         <v>106.1605</v>
@@ -22378,10 +22378,10 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H578" t="n">
-        <v>106.591</v>
+        <v>106.5911</v>
       </c>
     </row>
     <row r="579">
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H583" t="n">
-        <v>107.5751</v>
+        <v>107.5752</v>
       </c>
     </row>
     <row r="584">
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H584" t="n">
         <v>108.713</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H590" t="n">
         <v>110.3276</v>
@@ -22948,10 +22948,10 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H593" t="n">
-        <v>111.9268</v>
+        <v>111.9267</v>
       </c>
     </row>
     <row r="594">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H595" t="n">
         <v>110.0047</v>
@@ -23214,10 +23214,10 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H600" t="n">
-        <v>110.5428</v>
+        <v>110.5429</v>
       </c>
     </row>
     <row r="601">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H604" t="n">
         <v>112.5418</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H606" t="n">
         <v>114.4178</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H607" t="n">
         <v>113.5874</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H609" t="n">
         <v>115.0943</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H611" t="n">
         <v>116.3706</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H613" t="n">
         <v>115.9093</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H614" t="n">
         <v>116.0016</v>
@@ -24050,10 +24050,10 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H622" t="n">
-        <v>118.185</v>
+        <v>118.1851</v>
       </c>
     </row>
     <row r="623">
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H625" t="n">
         <v>115.1712</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H630" t="n">
         <v>114.1717</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H631" t="n">
         <v>113.7258</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.755482</v>
+        <v>53.755486</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57797,7 +57797,7 @@
         <v>53.784698</v>
       </c>
       <c r="H1510" t="n">
-        <v>100.0544</v>
+        <v>100.0543</v>
       </c>
     </row>
     <row r="1511">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.765228</v>
+        <v>53.765224</v>
       </c>
       <c r="H1511" t="n">
         <v>100.0181</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1512" t="n">
         <v>100.6158</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.284748</v>
+        <v>54.284752</v>
       </c>
       <c r="H1514" t="n">
         <v>100.9846</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.068439</v>
+        <v>54.068436</v>
       </c>
       <c r="H1517" t="n">
         <v>100.5822</v>
@@ -58139,7 +58139,7 @@
         <v>53.881622</v>
       </c>
       <c r="H1519" t="n">
-        <v>100.2347</v>
+        <v>100.2346</v>
       </c>
     </row>
     <row r="1520">
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1522" t="n">
         <v>99.66759999999999</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.12743</v>
+        <v>54.127434</v>
       </c>
       <c r="H1524" t="n">
         <v>100.6919</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1527" t="n">
         <v>102.9051</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1528" t="n">
         <v>103.399</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.562965</v>
+        <v>55.562962</v>
       </c>
       <c r="H1529" t="n">
         <v>103.3624</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.680958</v>
+        <v>55.680954</v>
       </c>
       <c r="H1532" t="n">
         <v>103.5819</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.051682</v>
+        <v>55.051678</v>
       </c>
       <c r="H1535" t="n">
         <v>102.4113</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.199165</v>
+        <v>55.199162</v>
       </c>
       <c r="H1538" t="n">
         <v>102.6856</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1541" t="n">
         <v>103.8014</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1545" t="n">
         <v>104.3867</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1549" t="n">
         <v>103.6002</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1550" t="n">
         <v>103.8014</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1551" t="n">
         <v>103.0332</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.907104</v>
+        <v>55.907101</v>
       </c>
       <c r="H1553" t="n">
         <v>104.0026</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1554" t="n">
         <v>105.3561</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1555" t="n">
         <v>106.1426</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0455</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1561" t="n">
         <v>102.3198</v>
@@ -59770,10 +59770,10 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>54.864861</v>
+        <v>54.864864</v>
       </c>
       <c r="H1562" t="n">
-        <v>102.0638</v>
+        <v>102.0637</v>
       </c>
     </row>
     <row r="1563">
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1563" t="n">
         <v>102.1918</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1564" t="n">
         <v>103.0515</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1566" t="n">
         <v>104.3501</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1568" t="n">
         <v>104.3501</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1573" t="n">
         <v>104.972</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1574" t="n">
         <v>104.8623</v>
@@ -60267,7 +60267,7 @@
         <v>56.39872</v>
       </c>
       <c r="H1575" t="n">
-        <v>104.9172</v>
+        <v>104.9171</v>
       </c>
     </row>
     <row r="1576">
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1578" t="n">
         <v>105.7138</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1580" t="n">
         <v>105.1448</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1582" t="n">
         <v>106.6314</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1583" t="n">
         <v>106.4295</v>
@@ -60723,7 +60723,7 @@
         <v>58.237751</v>
       </c>
       <c r="H1587" t="n">
-        <v>108.3383</v>
+        <v>108.3382</v>
       </c>
     </row>
     <row r="1588">
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1588" t="n">
         <v>109.311</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1592" t="n">
         <v>110.8526</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1593" t="n">
         <v>111.0362</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1595" t="n">
         <v>111.0729</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4394</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1604" t="n">
         <v>111.3665</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1613" t="n">
         <v>112.9632</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1614" t="n">
         <v>112.8898</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1622" t="n">
         <v>114.927</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1624" t="n">
         <v>114.5783</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1629" t="n">
         <v>110.1185</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1630" t="n">
         <v>111.5317</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1635" t="n">
         <v>109.7698</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1636" t="n">
         <v>109.1274</v>
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1637" t="n">
         <v>108.5218</v>
@@ -62927,7 +62927,7 @@
         <v>57.647194</v>
       </c>
       <c r="H1645" t="n">
-        <v>107.2397</v>
+        <v>107.2396</v>
       </c>
     </row>
     <row r="1646">
@@ -63649,7 +63649,7 @@
         <v>60.515209</v>
       </c>
       <c r="H1664" t="n">
-        <v>112.575</v>
+        <v>112.5749</v>
       </c>
     </row>
     <row r="1665">
@@ -64219,7 +64219,7 @@
         <v>60.139404</v>
       </c>
       <c r="H1679" t="n">
-        <v>111.8759</v>
+        <v>111.8758</v>
       </c>
     </row>
     <row r="1680">
@@ -64561,7 +64561,7 @@
         <v>62.196465</v>
       </c>
       <c r="H1688" t="n">
-        <v>115.7026</v>
+        <v>115.7025</v>
       </c>
     </row>
     <row r="1689">
@@ -64751,7 +64751,7 @@
         <v>62.196465</v>
       </c>
       <c r="H1693" t="n">
-        <v>115.7026</v>
+        <v>115.7025</v>
       </c>
     </row>
     <row r="1694">
@@ -64979,7 +64979,7 @@
         <v>63.027203</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.248</v>
+        <v>117.2479</v>
       </c>
     </row>
     <row r="1700">
@@ -65131,7 +65131,7 @@
         <v>63.360001</v>
       </c>
       <c r="H1703" t="n">
-        <v>117.8671</v>
+        <v>117.867</v>
       </c>
     </row>
     <row r="1704">
@@ -65397,7 +65397,7 @@
         <v>63.360001</v>
       </c>
       <c r="H1710" t="n">
-        <v>117.8671</v>
+        <v>117.867</v>
       </c>
     </row>
     <row r="1711">
@@ -65473,7 +65473,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1712" t="n">
-        <v>118.574</v>
+        <v>118.5739</v>
       </c>
     </row>
     <row r="1713">
@@ -65853,7 +65853,7 @@
         <v>64.110001</v>
       </c>
       <c r="H1722" t="n">
-        <v>119.2623</v>
+        <v>119.2622</v>
       </c>
     </row>
     <row r="1723">
@@ -65967,7 +65967,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1725" t="n">
-        <v>118.574</v>
+        <v>118.5739</v>
       </c>
     </row>
     <row r="1726">
@@ -66005,7 +66005,7 @@
         <v>64.110001</v>
       </c>
       <c r="H1726" t="n">
-        <v>119.2623</v>
+        <v>119.2622</v>
       </c>
     </row>
     <row r="1727">
@@ -66195,7 +66195,7 @@
         <v>64.489998</v>
       </c>
       <c r="H1731" t="n">
-        <v>119.9692</v>
+        <v>119.9691</v>
       </c>
     </row>
     <row r="1732">
@@ -66385,7 +66385,7 @@
         <v>65.56999999999999</v>
       </c>
       <c r="H1736" t="n">
-        <v>121.9783</v>
+        <v>121.9782</v>
       </c>
     </row>
     <row r="1737">
@@ -66423,7 +66423,7 @@
         <v>65.550003</v>
       </c>
       <c r="H1737" t="n">
-        <v>121.9411</v>
+        <v>121.941</v>
       </c>
     </row>
     <row r="1738">
@@ -66499,7 +66499,7 @@
         <v>65.91999800000001</v>
       </c>
       <c r="H1739" t="n">
-        <v>122.6294</v>
+        <v>122.6293</v>
       </c>
     </row>
     <row r="1740">
@@ -66537,7 +66537,7 @@
         <v>65.900002</v>
       </c>
       <c r="H1740" t="n">
-        <v>122.5922</v>
+        <v>122.5921</v>
       </c>
     </row>
     <row r="1741">
@@ -66575,7 +66575,7 @@
         <v>65.949997</v>
       </c>
       <c r="H1741" t="n">
-        <v>122.6852</v>
+        <v>122.6851</v>
       </c>
     </row>
     <row r="1742">
@@ -66613,7 +66613,7 @@
         <v>65.910004</v>
       </c>
       <c r="H1742" t="n">
-        <v>122.6108</v>
+        <v>122.6107</v>
       </c>
     </row>
     <row r="1743">
@@ -66651,7 +66651,7 @@
         <v>65.93000000000001</v>
       </c>
       <c r="H1743" t="n">
-        <v>122.648</v>
+        <v>122.6479</v>
       </c>
     </row>
     <row r="1744">
@@ -66765,7 +66765,7 @@
         <v>65.160004</v>
       </c>
       <c r="H1746" t="n">
-        <v>121.2156</v>
+        <v>121.2155</v>
       </c>
     </row>
     <row r="1747">
@@ -67031,7 +67031,7 @@
         <v>65.209999</v>
       </c>
       <c r="H1753" t="n">
-        <v>121.3086</v>
+        <v>121.3085</v>
       </c>
     </row>
     <row r="1754">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.084999</v>
+        <v>34.130001</v>
       </c>
       <c r="H253" t="n">
-        <v>112.9577</v>
+        <v>113.1069</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.415001</v>
+        <v>48.459999</v>
       </c>
       <c r="H504" t="n">
-        <v>136.9977</v>
+        <v>137.1251</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.051338</v>
+        <v>64.051331</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.411446</v>
+        <v>64.41145299999999</v>
       </c>
       <c r="H507" t="n">
         <v>100.5622</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.859161</v>
+        <v>64.859154</v>
       </c>
       <c r="H509" t="n">
         <v>101.2612</v>
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.77156100000001</v>
+        <v>64.771568</v>
       </c>
       <c r="H510" t="n">
-        <v>101.1244</v>
+        <v>101.1245</v>
       </c>
     </row>
     <row r="511">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.226524</v>
+        <v>64.226517</v>
       </c>
       <c r="H511" t="n">
         <v>100.2735</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H514" t="n">
         <v>101.1235</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H515" t="n">
         <v>101.0164</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.810097</v>
+        <v>64.810112</v>
       </c>
       <c r="H518" t="n">
         <v>101.1846</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.02555099999999</v>
+        <v>65.025558</v>
       </c>
       <c r="H521" t="n">
         <v>101.521</v>
@@ -20288,10 +20288,10 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H523" t="n">
-        <v>102.3007</v>
+        <v>102.3008</v>
       </c>
     </row>
     <row r="524">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H529" t="n">
         <v>101.8421</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H534" t="n">
         <v>102.2396</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H537" t="n">
         <v>103.5239</v>
@@ -20861,7 +20861,7 @@
         <v>66.435745</v>
       </c>
       <c r="H538" t="n">
-        <v>103.7226</v>
+        <v>103.7227</v>
       </c>
     </row>
     <row r="539">
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H539" t="n">
         <v>104.2578</v>
@@ -20937,7 +20937,7 @@
         <v>66.709946</v>
       </c>
       <c r="H540" t="n">
-        <v>104.1507</v>
+        <v>104.1508</v>
       </c>
     </row>
     <row r="541">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H541" t="n">
         <v>103.952</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H542" t="n">
         <v>104.2578</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H549" t="n">
         <v>104.1966</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H554" t="n">
         <v>104.2731</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H555" t="n">
         <v>103.2334</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H558" t="n">
         <v>103.4474</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H559" t="n">
         <v>103.8144</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H560" t="n">
         <v>104.2272</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H561" t="n">
         <v>105.1904</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H565" t="n">
         <v>104.9917</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.659859</v>
+        <v>67.659874</v>
       </c>
       <c r="H569" t="n">
         <v>105.6338</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.669662</v>
+        <v>67.66965500000001</v>
       </c>
       <c r="H570" t="n">
         <v>105.6491</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H571" t="n">
         <v>105.5421</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H574" t="n">
         <v>106.3983</v>
@@ -22264,10 +22264,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H575" t="n">
-        <v>105.4503</v>
+        <v>105.4504</v>
       </c>
     </row>
     <row r="576">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H576" t="n">
         <v>105.5574</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H577" t="n">
         <v>106.1605</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H578" t="n">
         <v>106.5911</v>
@@ -22495,7 +22495,7 @@
         <v>68.657104</v>
       </c>
       <c r="H581" t="n">
-        <v>107.1907</v>
+        <v>107.1908</v>
       </c>
     </row>
     <row r="582">
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H583" t="n">
         <v>107.5752</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H584" t="n">
         <v>108.713</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H590" t="n">
         <v>110.3276</v>
@@ -22948,10 +22948,10 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H593" t="n">
-        <v>111.9267</v>
+        <v>111.9268</v>
       </c>
     </row>
     <row r="594">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H595" t="n">
         <v>110.0047</v>
@@ -23065,7 +23065,7 @@
         <v>70.76477800000001</v>
       </c>
       <c r="H596" t="n">
-        <v>110.4813</v>
+        <v>110.4814</v>
       </c>
     </row>
     <row r="597">
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H600" t="n">
         <v>110.5429</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H604" t="n">
         <v>112.5418</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H606" t="n">
         <v>114.4178</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H607" t="n">
         <v>113.5874</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H609" t="n">
         <v>115.0943</v>
@@ -23597,7 +23597,7 @@
         <v>73.97554</v>
       </c>
       <c r="H610" t="n">
-        <v>115.4941</v>
+        <v>115.4942</v>
       </c>
     </row>
     <row r="611">
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H611" t="n">
         <v>116.3706</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H613" t="n">
         <v>115.9093</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H614" t="n">
         <v>116.0016</v>
@@ -23939,7 +23939,7 @@
         <v>74.940735</v>
       </c>
       <c r="H619" t="n">
-        <v>117.001</v>
+        <v>117.0011</v>
       </c>
     </row>
     <row r="620">
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H622" t="n">
         <v>118.1851</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H625" t="n">
         <v>115.1712</v>
@@ -24205,7 +24205,7 @@
         <v>74.271011</v>
       </c>
       <c r="H626" t="n">
-        <v>115.9554</v>
+        <v>115.9555</v>
       </c>
     </row>
     <row r="627">
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H630" t="n">
         <v>114.1717</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H631" t="n">
         <v>113.7258</v>
@@ -24433,7 +24433,7 @@
         <v>72.96109800000001</v>
       </c>
       <c r="H632" t="n">
-        <v>113.9103</v>
+        <v>113.9104</v>
       </c>
     </row>
     <row r="633">
@@ -24585,7 +24585,7 @@
         <v>71.91392500000001</v>
       </c>
       <c r="H636" t="n">
-        <v>112.2754</v>
+        <v>112.2755</v>
       </c>
     </row>
     <row r="637">
@@ -24699,7 +24699,7 @@
         <v>71.805038</v>
       </c>
       <c r="H639" t="n">
-        <v>112.1054</v>
+        <v>112.1055</v>
       </c>
     </row>
     <row r="640">
@@ -24813,7 +24813,7 @@
         <v>71.805038</v>
       </c>
       <c r="H642" t="n">
-        <v>112.1054</v>
+        <v>112.1055</v>
       </c>
     </row>
     <row r="643">
@@ -24889,7 +24889,7 @@
         <v>72.389061</v>
       </c>
       <c r="H644" t="n">
-        <v>113.0172</v>
+        <v>113.0173</v>
       </c>
     </row>
     <row r="645">
@@ -24965,7 +24965,7 @@
         <v>73.171059</v>
       </c>
       <c r="H646" t="n">
-        <v>114.2381</v>
+        <v>114.2382</v>
       </c>
     </row>
     <row r="647">
@@ -26029,7 +26029,7 @@
         <v>75.467552</v>
       </c>
       <c r="H674" t="n">
-        <v>117.8235</v>
+        <v>117.8236</v>
       </c>
     </row>
     <row r="675">
@@ -26219,7 +26219,7 @@
         <v>76.96225699999999</v>
       </c>
       <c r="H679" t="n">
-        <v>120.1571</v>
+        <v>120.1572</v>
       </c>
     </row>
     <row r="680">
@@ -26257,7 +26257,7 @@
         <v>77.526482</v>
       </c>
       <c r="H680" t="n">
-        <v>121.038</v>
+        <v>121.0381</v>
       </c>
     </row>
     <row r="681">
@@ -26485,7 +26485,7 @@
         <v>77.199821</v>
       </c>
       <c r="H686" t="n">
-        <v>120.528</v>
+        <v>120.5281</v>
       </c>
     </row>
     <row r="687">
@@ -26713,7 +26713,7 @@
         <v>76.853371</v>
       </c>
       <c r="H692" t="n">
-        <v>119.9871</v>
+        <v>119.9872</v>
       </c>
     </row>
     <row r="693">
@@ -26941,7 +26941,7 @@
         <v>78.58000199999999</v>
       </c>
       <c r="H698" t="n">
-        <v>122.6828</v>
+        <v>122.6829</v>
       </c>
     </row>
     <row r="699">
@@ -26979,7 +26979,7 @@
         <v>78.349998</v>
       </c>
       <c r="H699" t="n">
-        <v>122.3237</v>
+        <v>122.3238</v>
       </c>
     </row>
     <row r="700">
@@ -27017,7 +27017,7 @@
         <v>78.980003</v>
       </c>
       <c r="H700" t="n">
-        <v>123.3073</v>
+        <v>123.3074</v>
       </c>
     </row>
     <row r="701">
@@ -27169,7 +27169,7 @@
         <v>78.81999999999999</v>
       </c>
       <c r="H704" t="n">
-        <v>123.0575</v>
+        <v>123.0576</v>
       </c>
     </row>
     <row r="705">
@@ -27625,7 +27625,7 @@
         <v>79.949997</v>
       </c>
       <c r="H716" t="n">
-        <v>124.8217</v>
+        <v>124.8218</v>
       </c>
     </row>
     <row r="717">
@@ -28347,7 +28347,7 @@
         <v>81.629997</v>
       </c>
       <c r="H735" t="n">
-        <v>127.4446</v>
+        <v>127.4447</v>
       </c>
     </row>
     <row r="736">
@@ -28537,7 +28537,7 @@
         <v>81.620003</v>
       </c>
       <c r="H740" t="n">
-        <v>127.429</v>
+        <v>127.4291</v>
       </c>
     </row>
     <row r="741">
@@ -28575,7 +28575,7 @@
         <v>81.300003</v>
       </c>
       <c r="H741" t="n">
-        <v>126.9294</v>
+        <v>126.9295</v>
       </c>
     </row>
     <row r="742">
@@ -28917,7 +28917,7 @@
         <v>81.389999</v>
       </c>
       <c r="H750" t="n">
-        <v>127.0699</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="751">
@@ -29069,13 +29069,13 @@
         <v>82.110001</v>
       </c>
       <c r="H754" t="n">
-        <v>128.194</v>
+        <v>128.1941</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.81999999999999</v>
+        <v>81.739998</v>
       </c>
       <c r="H755" t="n">
-        <v>127.7413</v>
+        <v>127.6164</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.330002</v>
+        <v>127.339996</v>
       </c>
       <c r="H1006" t="n">
-        <v>121.0476</v>
+        <v>121.0571</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.330002</v>
+        <v>127.339996</v>
       </c>
       <c r="H1257" t="n">
-        <v>121.0476</v>
+        <v>121.0571</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.330002</v>
+        <v>127.339996</v>
       </c>
       <c r="H1508" t="n">
-        <v>121.0476</v>
+        <v>121.0571</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.755486</v>
+        <v>53.755489</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.655476</v>
+        <v>53.655479</v>
       </c>
       <c r="H1515" t="n">
         <v>99.81399999999999</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.645645</v>
+        <v>53.645649</v>
       </c>
       <c r="H1516" t="n">
         <v>99.7957</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.068436</v>
+        <v>54.068439</v>
       </c>
       <c r="H1517" t="n">
         <v>100.5822</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.127434</v>
+        <v>54.12743</v>
       </c>
       <c r="H1524" t="n">
         <v>100.6919</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1527" t="n">
         <v>102.9051</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.494137</v>
+        <v>55.494133</v>
       </c>
       <c r="H1530" t="n">
         <v>103.2344</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.051678</v>
+        <v>55.051682</v>
       </c>
       <c r="H1535" t="n">
         <v>102.4113</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.336819</v>
+        <v>55.336815</v>
       </c>
       <c r="H1536" t="n">
         <v>102.9417</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1537" t="n">
         <v>103.7648</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.199162</v>
+        <v>55.199165</v>
       </c>
       <c r="H1538" t="n">
         <v>102.6856</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1539" t="n">
         <v>103.7648</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1541" t="n">
         <v>103.8014</v>
@@ -59048,10 +59048,10 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1543" t="n">
-        <v>104.6977</v>
+        <v>104.6976</v>
       </c>
     </row>
     <row r="1544">
@@ -59086,10 +59086,10 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1544" t="n">
-        <v>104.4782</v>
+        <v>104.4781</v>
       </c>
     </row>
     <row r="1545">
@@ -59165,7 +59165,7 @@
         <v>56.054585</v>
       </c>
       <c r="H1546" t="n">
-        <v>104.277</v>
+        <v>104.2769</v>
       </c>
     </row>
     <row r="1547">
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.818607</v>
+        <v>55.818611</v>
       </c>
       <c r="H1547" t="n">
         <v>103.838</v>
@@ -59241,7 +59241,7 @@
         <v>55.848106</v>
       </c>
       <c r="H1548" t="n">
-        <v>103.8929</v>
+        <v>103.8928</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1550" t="n">
         <v>103.8014</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1563" t="n">
         <v>102.1918</v>
@@ -59887,7 +59887,7 @@
         <v>56.054585</v>
       </c>
       <c r="H1565" t="n">
-        <v>104.277</v>
+        <v>104.2769</v>
       </c>
     </row>
     <row r="1566">
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1566" t="n">
         <v>104.3501</v>
@@ -59960,10 +59960,10 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1567" t="n">
-        <v>104.6977</v>
+        <v>104.6976</v>
       </c>
     </row>
     <row r="1568">
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1568" t="n">
         <v>104.3501</v>
@@ -60036,10 +60036,10 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1569" t="n">
-        <v>104.4782</v>
+        <v>104.4781</v>
       </c>
     </row>
     <row r="1570">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.487213</v>
+        <v>56.487217</v>
       </c>
       <c r="H1571" t="n">
         <v>105.0818</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.39872</v>
+        <v>56.398724</v>
       </c>
       <c r="H1575" t="n">
         <v>104.9171</v>
@@ -60378,10 +60378,10 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>56.826942</v>
+        <v>56.826939</v>
       </c>
       <c r="H1578" t="n">
-        <v>105.7138</v>
+        <v>105.7137</v>
       </c>
     </row>
     <row r="1579">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>56.521107</v>
+        <v>56.521103</v>
       </c>
       <c r="H1580" t="n">
         <v>105.1448</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>57.320229</v>
+        <v>57.320232</v>
       </c>
       <c r="H1582" t="n">
         <v>106.6314</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>57.211708</v>
+        <v>57.211712</v>
       </c>
       <c r="H1583" t="n">
         <v>106.4295</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.760635</v>
+        <v>58.760639</v>
       </c>
       <c r="H1588" t="n">
         <v>109.311</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.589363</v>
+        <v>59.589367</v>
       </c>
       <c r="H1592" t="n">
         <v>110.8526</v>
@@ -60948,10 +60948,10 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.688023</v>
+        <v>59.688019</v>
       </c>
       <c r="H1593" t="n">
-        <v>111.0362</v>
+        <v>111.0361</v>
       </c>
     </row>
     <row r="1594">
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.707752</v>
+        <v>59.707756</v>
       </c>
       <c r="H1595" t="n">
         <v>111.0729</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>58.8297</v>
+        <v>58.829697</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4394</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.865608</v>
+        <v>59.865604</v>
       </c>
       <c r="H1604" t="n">
         <v>111.3665</v>
@@ -61407,7 +61407,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1605" t="n">
-        <v>110.4856</v>
+        <v>110.4855</v>
       </c>
     </row>
     <row r="1606">
@@ -61559,7 +61559,7 @@
         <v>60.339165</v>
       </c>
       <c r="H1609" t="n">
-        <v>112.2475</v>
+        <v>112.2474</v>
       </c>
     </row>
     <row r="1610">
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.72393</v>
+        <v>60.723927</v>
       </c>
       <c r="H1613" t="n">
         <v>112.9632</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.684464</v>
+        <v>60.684467</v>
       </c>
       <c r="H1614" t="n">
         <v>112.8898</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>61.779568</v>
+        <v>61.779564</v>
       </c>
       <c r="H1622" t="n">
         <v>114.927</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>61.592121</v>
+        <v>61.592117</v>
       </c>
       <c r="H1624" t="n">
         <v>114.5783</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.194729</v>
+        <v>59.194733</v>
       </c>
       <c r="H1629" t="n">
         <v>110.1185</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.954395</v>
+        <v>59.954399</v>
       </c>
       <c r="H1630" t="n">
         <v>111.5317</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>59.007286</v>
+        <v>59.007282</v>
       </c>
       <c r="H1635" t="n">
         <v>109.7698</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>58.66198</v>
+        <v>58.661976</v>
       </c>
       <c r="H1636" t="n">
         <v>109.1274</v>
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>58.336407</v>
+        <v>58.336411</v>
       </c>
       <c r="H1637" t="n">
         <v>108.5218</v>
@@ -63383,7 +63383,7 @@
         <v>60.910801</v>
       </c>
       <c r="H1657" t="n">
-        <v>113.3109</v>
+        <v>113.3108</v>
       </c>
     </row>
     <row r="1658">
@@ -63877,7 +63877,7 @@
         <v>59.684475</v>
       </c>
       <c r="H1670" t="n">
-        <v>111.0296</v>
+        <v>111.0295</v>
       </c>
     </row>
     <row r="1671">
@@ -64409,7 +64409,7 @@
         <v>62.186577</v>
       </c>
       <c r="H1684" t="n">
-        <v>115.6842</v>
+        <v>115.6841</v>
       </c>
     </row>
     <row r="1685">
@@ -65587,7 +65587,7 @@
         <v>64.860001</v>
       </c>
       <c r="H1715" t="n">
-        <v>120.6575</v>
+        <v>120.6574</v>
       </c>
     </row>
     <row r="1716">
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>64.970001</v>
+        <v>64.980003</v>
       </c>
       <c r="H1760" t="n">
-        <v>120.8621</v>
+        <v>120.8807</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.130001</v>
+        <v>33.509998</v>
       </c>
       <c r="H253" t="n">
-        <v>113.1069</v>
+        <v>111.0522</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.459999</v>
+        <v>48.564999</v>
       </c>
       <c r="H504" t="n">
-        <v>137.1251</v>
+        <v>137.4222</v>
       </c>
     </row>
     <row r="505">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.97595200000001</v>
+        <v>64.975945</v>
       </c>
       <c r="H508" t="n">
         <v>101.4436</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H510" t="n">
         <v>101.1245</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.226517</v>
+        <v>64.226524</v>
       </c>
       <c r="H511" t="n">
         <v>100.2735</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.810112</v>
+        <v>64.810104</v>
       </c>
       <c r="H518" t="n">
         <v>101.1846</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H519" t="n">
         <v>101.6433</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.035347</v>
+        <v>65.035355</v>
       </c>
       <c r="H520" t="n">
         <v>101.5363</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H521" t="n">
         <v>101.521</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H534" t="n">
         <v>102.2396</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H537" t="n">
         <v>103.5239</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H541" t="n">
         <v>103.952</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.66098</v>
+        <v>66.660988</v>
       </c>
       <c r="H546" t="n">
         <v>104.0743</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.357399</v>
+        <v>66.35740699999999</v>
       </c>
       <c r="H547" t="n">
-        <v>103.6003</v>
+        <v>103.6004</v>
       </c>
     </row>
     <row r="548">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H551" t="n">
         <v>106.0772</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H557" t="n">
         <v>103.6615</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H567" t="n">
         <v>105.7714</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H568" t="n">
         <v>106.0008</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.659874</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.6338</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H570" t="n">
         <v>105.6491</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H571" t="n">
         <v>105.5421</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H576" t="n">
         <v>105.5574</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.739998</v>
+        <v>81.730003</v>
       </c>
       <c r="H755" t="n">
-        <v>127.6164</v>
+        <v>127.6008</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.339996</v>
+        <v>127.169998</v>
       </c>
       <c r="H1006" t="n">
-        <v>121.0571</v>
+        <v>120.8955</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.339996</v>
+        <v>127.169998</v>
       </c>
       <c r="H1257" t="n">
-        <v>121.0571</v>
+        <v>120.8955</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.339996</v>
+        <v>127.169998</v>
       </c>
       <c r="H1508" t="n">
-        <v>121.0571</v>
+        <v>120.8955</v>
       </c>
     </row>
     <row r="1509">
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.086533</v>
+        <v>54.086529</v>
       </c>
       <c r="H1512" t="n">
         <v>100.6158</v>
@@ -57984,10 +57984,10 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.655479</v>
+        <v>53.655476</v>
       </c>
       <c r="H1515" t="n">
-        <v>99.81399999999999</v>
+        <v>99.8139</v>
       </c>
     </row>
     <row r="1516">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.562962</v>
+        <v>55.562965</v>
       </c>
       <c r="H1529" t="n">
         <v>103.3624</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.494133</v>
+        <v>55.494137</v>
       </c>
       <c r="H1530" t="n">
         <v>103.2344</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.051682</v>
+        <v>55.051685</v>
       </c>
       <c r="H1535" t="n">
         <v>102.4113</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.336815</v>
+        <v>55.336819</v>
       </c>
       <c r="H1536" t="n">
         <v>102.9417</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.798943</v>
+        <v>55.798939</v>
       </c>
       <c r="H1541" t="n">
         <v>103.8014</v>
@@ -59048,10 +59048,10 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1543" t="n">
-        <v>104.6976</v>
+        <v>104.6977</v>
       </c>
     </row>
     <row r="1544">
@@ -59086,10 +59086,10 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1544" t="n">
-        <v>104.4781</v>
+        <v>104.4782</v>
       </c>
     </row>
     <row r="1545">
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.113583</v>
+        <v>56.113579</v>
       </c>
       <c r="H1545" t="n">
         <v>104.3867</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.798943</v>
+        <v>55.798939</v>
       </c>
       <c r="H1550" t="n">
         <v>103.8014</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>56.634697</v>
+        <v>56.634693</v>
       </c>
       <c r="H1554" t="n">
         <v>105.3561</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.133244</v>
+        <v>56.133247</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4233</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1564" t="n">
         <v>103.0515</v>
@@ -59960,10 +59960,10 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1567" t="n">
-        <v>104.6976</v>
+        <v>104.6977</v>
       </c>
     </row>
     <row r="1568">
@@ -60036,10 +60036,10 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1569" t="n">
-        <v>104.4781</v>
+        <v>104.4782</v>
       </c>
     </row>
     <row r="1570">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.487217</v>
+        <v>56.487213</v>
       </c>
       <c r="H1571" t="n">
         <v>105.0818</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1572" t="n">
         <v>105.1366</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.428219</v>
+        <v>56.428215</v>
       </c>
       <c r="H1573" t="n">
         <v>104.972</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.369225</v>
+        <v>56.369221</v>
       </c>
       <c r="H1574" t="n">
         <v>104.8623</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.398724</v>
+        <v>56.39872</v>
       </c>
       <c r="H1575" t="n">
         <v>104.9171</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1576" t="n">
         <v>105.4842</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>64.980003</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="H1760" t="n">
-        <v>120.8807</v>
+        <v>120.7877</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.32384500000001</v>
+        <v>64.323853</v>
       </c>
       <c r="H506" t="n">
         <v>100.4255</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.41145299999999</v>
+        <v>64.411438</v>
       </c>
       <c r="H507" t="n">
         <v>100.5622</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.226524</v>
+        <v>64.226517</v>
       </c>
       <c r="H511" t="n">
         <v>100.2735</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.489311</v>
+        <v>64.489304</v>
       </c>
       <c r="H512" t="n">
         <v>100.6838</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H514" t="n">
         <v>101.1235</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H515" t="n">
-        <v>101.0164</v>
+        <v>101.0165</v>
       </c>
     </row>
     <row r="516">
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H518" t="n">
         <v>101.1846</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H519" t="n">
         <v>101.6433</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.035355</v>
+        <v>65.035347</v>
       </c>
       <c r="H520" t="n">
         <v>101.5363</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H523" t="n">
         <v>102.3008</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H529" t="n">
         <v>101.8421</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H539" t="n">
         <v>104.2578</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H542" t="n">
         <v>104.2578</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.660988</v>
+        <v>66.66098</v>
       </c>
       <c r="H546" t="n">
         <v>104.0743</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.35740699999999</v>
+        <v>66.357399</v>
       </c>
       <c r="H547" t="n">
-        <v>103.6004</v>
+        <v>103.6003</v>
       </c>
     </row>
     <row r="548">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H549" t="n">
         <v>104.1966</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H551" t="n">
         <v>106.0772</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H554" t="n">
         <v>104.2731</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H555" t="n">
         <v>103.2334</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H557" t="n">
         <v>103.6615</v>
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H558" t="n">
-        <v>103.4474</v>
+        <v>103.4475</v>
       </c>
     </row>
     <row r="559">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H559" t="n">
         <v>103.8144</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.2272</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H561" t="n">
         <v>105.1904</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H565" t="n">
         <v>104.9917</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H567" t="n">
         <v>105.7714</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H568" t="n">
         <v>106.0008</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H569" t="n">
         <v>105.6338</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H574" t="n">
         <v>106.3983</v>
@@ -22264,10 +22264,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H575" t="n">
-        <v>105.4504</v>
+        <v>105.4503</v>
       </c>
     </row>
     <row r="576">
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H577" t="n">
         <v>106.1605</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H578" t="n">
         <v>106.5911</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H583" t="n">
         <v>107.5752</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H584" t="n">
         <v>108.713</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H590" t="n">
         <v>110.3276</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H593" t="n">
         <v>111.9268</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H595" t="n">
         <v>110.0047</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H600" t="n">
         <v>110.5429</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H604" t="n">
         <v>112.5418</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H606" t="n">
         <v>114.4178</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H607" t="n">
         <v>113.5874</v>
@@ -23556,10 +23556,10 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H609" t="n">
-        <v>115.0943</v>
+        <v>115.0944</v>
       </c>
     </row>
     <row r="610">
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H611" t="n">
         <v>116.3706</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H613" t="n">
         <v>115.9093</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H614" t="n">
         <v>116.0016</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H622" t="n">
         <v>118.1851</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H625" t="n">
         <v>115.1712</v>
@@ -24354,10 +24354,10 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H630" t="n">
-        <v>114.1717</v>
+        <v>114.1718</v>
       </c>
     </row>
     <row r="631">
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H631" t="n">
         <v>113.7258</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.755489</v>
+        <v>53.755486</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1512" t="n">
         <v>100.6158</v>
@@ -57987,7 +57987,7 @@
         <v>53.655476</v>
       </c>
       <c r="H1515" t="n">
-        <v>99.8139</v>
+        <v>99.81399999999999</v>
       </c>
     </row>
     <row r="1516">
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.645649</v>
+        <v>53.645645</v>
       </c>
       <c r="H1516" t="n">
         <v>99.7957</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>53.999607</v>
+        <v>53.999611</v>
       </c>
       <c r="H1518" t="n">
         <v>100.4541</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.02911</v>
+        <v>54.029106</v>
       </c>
       <c r="H1523" t="n">
         <v>100.509</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.012352</v>
+        <v>55.012348</v>
       </c>
       <c r="H1526" t="n">
         <v>102.3381</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1527" t="n">
         <v>102.9051</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1528" t="n">
         <v>103.399</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1532" t="n">
         <v>103.5819</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>54.943523</v>
+        <v>54.943527</v>
       </c>
       <c r="H1533" t="n">
         <v>102.2101</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.25816</v>
+        <v>55.258163</v>
       </c>
       <c r="H1534" t="n">
         <v>102.7954</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.051685</v>
+        <v>55.051682</v>
       </c>
       <c r="H1535" t="n">
         <v>102.4113</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.798939</v>
+        <v>55.798946</v>
       </c>
       <c r="H1541" t="n">
         <v>103.8014</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1545" t="n">
         <v>104.3867</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1546" t="n">
         <v>104.2769</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.818611</v>
+        <v>55.818607</v>
       </c>
       <c r="H1547" t="n">
         <v>103.838</v>
@@ -59241,7 +59241,7 @@
         <v>55.848106</v>
       </c>
       <c r="H1548" t="n">
-        <v>103.8928</v>
+        <v>103.8929</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.798939</v>
+        <v>55.798946</v>
       </c>
       <c r="H1550" t="n">
         <v>103.8014</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1554" t="n">
         <v>105.3561</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.133247</v>
+        <v>56.133244</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4233</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0455</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>54.80587</v>
+        <v>54.805866</v>
       </c>
       <c r="H1560" t="n">
         <v>101.954</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1563" t="n">
         <v>102.1918</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1564" t="n">
         <v>103.0515</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1565" t="n">
         <v>104.2769</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1566" t="n">
         <v>104.3501</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1568" t="n">
         <v>104.3501</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1573" t="n">
         <v>104.972</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1574" t="n">
         <v>104.8623</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1576" t="n">
         <v>105.4842</v>
@@ -60378,10 +60378,10 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1578" t="n">
-        <v>105.7137</v>
+        <v>105.7138</v>
       </c>
     </row>
     <row r="1579">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1580" t="n">
         <v>105.1448</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1582" t="n">
         <v>106.6314</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1583" t="n">
         <v>106.4295</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1588" t="n">
         <v>109.311</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1592" t="n">
         <v>110.8526</v>
@@ -60948,10 +60948,10 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1593" t="n">
-        <v>111.0361</v>
+        <v>111.0362</v>
       </c>
     </row>
     <row r="1594">
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1595" t="n">
         <v>111.0729</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4394</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1604" t="n">
         <v>111.3665</v>
@@ -61407,7 +61407,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1605" t="n">
-        <v>110.4855</v>
+        <v>110.4856</v>
       </c>
     </row>
     <row r="1606">
@@ -61559,7 +61559,7 @@
         <v>60.339165</v>
       </c>
       <c r="H1609" t="n">
-        <v>112.2474</v>
+        <v>112.2475</v>
       </c>
     </row>
     <row r="1610">
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1613" t="n">
         <v>112.9632</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1614" t="n">
         <v>112.8898</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1622" t="n">
         <v>114.927</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1624" t="n">
         <v>114.5783</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1629" t="n">
         <v>110.1185</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1630" t="n">
         <v>111.5317</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1635" t="n">
         <v>109.7698</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1636" t="n">
         <v>109.1274</v>
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1637" t="n">
         <v>108.5218</v>
@@ -63383,7 +63383,7 @@
         <v>60.910801</v>
       </c>
       <c r="H1657" t="n">
-        <v>113.3108</v>
+        <v>113.3109</v>
       </c>
     </row>
     <row r="1658">
@@ -63877,7 +63877,7 @@
         <v>59.684475</v>
       </c>
       <c r="H1670" t="n">
-        <v>111.0295</v>
+        <v>111.0296</v>
       </c>
     </row>
     <row r="1671">
@@ -64409,7 +64409,7 @@
         <v>62.186577</v>
       </c>
       <c r="H1684" t="n">
-        <v>115.6841</v>
+        <v>115.6842</v>
       </c>
     </row>
     <row r="1685">
@@ -65587,7 +65587,7 @@
         <v>64.860001</v>
       </c>
       <c r="H1715" t="n">
-        <v>120.6574</v>
+        <v>120.6575</v>
       </c>
     </row>
     <row r="1716">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>33.384998</v>
+        <v>33.125</v>
       </c>
       <c r="H253" t="n">
-        <v>110.0725</v>
+        <v>109.2153</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.264999</v>
+        <v>48.279999</v>
       </c>
       <c r="H504" t="n">
-        <v>135.4047</v>
+        <v>135.4468</v>
       </c>
     </row>
     <row r="505">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.489304</v>
+        <v>64.489311</v>
       </c>
       <c r="H511" t="n">
         <v>100.2572</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H513" t="n">
         <v>100.695</v>
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>64.810112</v>
+        <v>64.810104</v>
       </c>
       <c r="H517" t="n">
-        <v>100.756</v>
+        <v>100.7559</v>
       </c>
     </row>
     <row r="518">
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H518" t="n">
         <v>101.2127</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H520" t="n">
         <v>101.0909</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H530" t="n">
         <v>101.7912</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H532" t="n">
         <v>102.4915</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H533" t="n">
         <v>101.8064</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H534" t="n">
-        <v>102.933</v>
+        <v>102.9331</v>
       </c>
     </row>
     <row r="535">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H536" t="n">
         <v>103.0853</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H538" t="n">
         <v>103.8161</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H540" t="n">
         <v>103.5116</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H541" t="n">
         <v>103.8161</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H550" t="n">
         <v>105.6278</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H552" t="n">
         <v>104.3946</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H553" t="n">
         <v>103.8313</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H556" t="n">
         <v>103.2223</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H557" t="n">
         <v>103.0092</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H558" t="n">
         <v>103.3746</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.7448</v>
@@ -21846,10 +21846,10 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H564" t="n">
-        <v>104.5468</v>
+        <v>104.5469</v>
       </c>
     </row>
     <row r="565">
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H566" t="n">
         <v>105.3233</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H567" t="n">
         <v>105.5517</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.659874</v>
+        <v>67.659859</v>
       </c>
       <c r="H568" t="n">
         <v>105.1863</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H569" t="n">
         <v>105.2015</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H570" t="n">
         <v>105.0949</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H573" t="n">
         <v>105.9475</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H575" t="n">
         <v>105.1102</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H576" t="n">
         <v>105.7107</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H577" t="n">
         <v>106.1395</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H582" t="n">
         <v>107.1194</v>
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H583" t="n">
-        <v>108.2525</v>
+        <v>108.2524</v>
       </c>
     </row>
     <row r="584">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H589" t="n">
         <v>109.8602</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H592" t="n">
         <v>111.4526</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H594" t="n">
         <v>109.5386</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H599" t="n">
         <v>110.0745</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H603" t="n">
         <v>112.065</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H605" t="n">
         <v>113.933</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H606" t="n">
         <v>113.1062</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H608" t="n">
         <v>114.6067</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H610" t="n">
         <v>115.8776</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H612" t="n">
         <v>115.4182</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H613" t="n">
         <v>115.5101</v>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H621" t="n">
-        <v>117.6843</v>
+        <v>117.6844</v>
       </c>
     </row>
     <row r="622">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H624" t="n">
         <v>114.6833</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H629" t="n">
         <v>113.688</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H630" t="n">
         <v>113.244</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.239998</v>
+        <v>81.040001</v>
       </c>
       <c r="H755" t="n">
-        <v>126.2984</v>
+        <v>125.9875</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.400002</v>
+        <v>126.029999</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.1293</v>
+        <v>119.7776</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.400002</v>
+        <v>126.029999</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.1293</v>
+        <v>119.7776</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.400002</v>
+        <v>126.029999</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.1293</v>
+        <v>119.7776</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.784695</v>
+        <v>53.784698</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.765228</v>
+        <v>53.765224</v>
       </c>
       <c r="H1510" t="n">
         <v>99.96380000000001</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.028111</v>
+        <v>54.028114</v>
       </c>
       <c r="H1512" t="n">
         <v>100.4526</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.284748</v>
+        <v>54.284752</v>
       </c>
       <c r="H1513" t="n">
         <v>100.9297</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.645645</v>
+        <v>53.645649</v>
       </c>
       <c r="H1515" t="n">
         <v>99.7415</v>
@@ -58025,7 +58025,7 @@
         <v>54.068439</v>
       </c>
       <c r="H1516" t="n">
-        <v>100.5276</v>
+        <v>100.5275</v>
       </c>
     </row>
     <row r="1517">
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1521" t="n">
         <v>99.6135</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1527" t="n">
         <v>103.3428</v>
@@ -58592,10 +58592,10 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.680958</v>
+        <v>55.680954</v>
       </c>
       <c r="H1531" t="n">
-        <v>103.5257</v>
+        <v>103.5256</v>
       </c>
     </row>
     <row r="1532">
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.051682</v>
+        <v>55.051685</v>
       </c>
       <c r="H1534" t="n">
         <v>102.3557</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1536" t="n">
         <v>103.7085</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1538" t="n">
         <v>103.7085</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.798943</v>
+        <v>55.798939</v>
       </c>
       <c r="H1540" t="n">
         <v>103.745</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.818607</v>
+        <v>55.818611</v>
       </c>
       <c r="H1546" t="n">
         <v>103.7816</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1548" t="n">
         <v>103.5439</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.798943</v>
+        <v>55.798939</v>
       </c>
       <c r="H1549" t="n">
         <v>103.745</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1550" t="n">
         <v>102.9772</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.907104</v>
+        <v>55.907101</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9461</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1554" t="n">
         <v>106.085</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.133244</v>
+        <v>56.133247</v>
       </c>
       <c r="H1556" t="n">
         <v>104.3666</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1558" t="n">
         <v>101.99</v>
@@ -59694,10 +59694,10 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1560" t="n">
-        <v>102.2643</v>
+        <v>102.2642</v>
       </c>
     </row>
     <row r="1561">
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.864861</v>
+        <v>54.864864</v>
       </c>
       <c r="H1561" t="n">
         <v>102.0083</v>
@@ -59887,7 +59887,7 @@
         <v>56.093914</v>
       </c>
       <c r="H1565" t="n">
-        <v>104.2935</v>
+        <v>104.2934</v>
       </c>
     </row>
     <row r="1566">
@@ -59963,7 +59963,7 @@
         <v>56.093914</v>
       </c>
       <c r="H1567" t="n">
-        <v>104.2935</v>
+        <v>104.2934</v>
       </c>
     </row>
     <row r="1568">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1571" t="n">
         <v>105.0795</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1575" t="n">
         <v>105.4269</v>
@@ -61369,7 +61369,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1604" t="n">
-        <v>110.4256</v>
+        <v>110.4255</v>
       </c>
     </row>
     <row r="1605">
@@ -61901,7 +61901,7 @@
         <v>60.832455</v>
       </c>
       <c r="H1618" t="n">
-        <v>113.1037</v>
+        <v>113.1036</v>
       </c>
     </row>
     <row r="1619">
@@ -63383,7 +63383,7 @@
         <v>60.722897</v>
       </c>
       <c r="H1657" t="n">
-        <v>112.9</v>
+        <v>112.8999</v>
       </c>
     </row>
     <row r="1658">
@@ -63535,7 +63535,7 @@
         <v>60.64378</v>
       </c>
       <c r="H1661" t="n">
-        <v>112.7529</v>
+        <v>112.7528</v>
       </c>
     </row>
     <row r="1662">
@@ -63573,7 +63573,7 @@
         <v>60.485542</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.4587</v>
+        <v>112.4586</v>
       </c>
     </row>
     <row r="1663">
@@ -63839,7 +63839,7 @@
         <v>59.684475</v>
       </c>
       <c r="H1669" t="n">
-        <v>110.9693</v>
+        <v>110.9692</v>
       </c>
     </row>
     <row r="1670">
@@ -65321,7 +65321,7 @@
         <v>63.330002</v>
       </c>
       <c r="H1708" t="n">
-        <v>117.7473</v>
+        <v>117.7472</v>
       </c>
     </row>
     <row r="1709">
@@ -65435,7 +65435,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1711" t="n">
-        <v>118.5096</v>
+        <v>118.5095</v>
       </c>
     </row>
     <row r="1712">
@@ -65929,7 +65929,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1724" t="n">
-        <v>118.5096</v>
+        <v>118.5095</v>
       </c>
     </row>
     <row r="1725">
@@ -66689,7 +66689,7 @@
         <v>65.629997</v>
       </c>
       <c r="H1744" t="n">
-        <v>122.0236</v>
+        <v>122.0235</v>
       </c>
     </row>
     <row r="1745">
@@ -66955,7 +66955,7 @@
         <v>65.629997</v>
       </c>
       <c r="H1751" t="n">
-        <v>122.0236</v>
+        <v>122.0235</v>
       </c>
     </row>
     <row r="1752">
@@ -67031,7 +67031,7 @@
         <v>65.510002</v>
       </c>
       <c r="H1753" t="n">
-        <v>121.8005</v>
+        <v>121.8004</v>
       </c>
     </row>
     <row r="1754">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>64.160004</v>
+        <v>64.010002</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.2904</v>
+        <v>119.0115</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.41145299999999</v>
+        <v>64.411438</v>
       </c>
       <c r="H506" t="n">
         <v>100.1362</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.975945</v>
+        <v>64.97595200000001</v>
       </c>
       <c r="H507" t="n">
         <v>101.0138</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H509" t="n">
         <v>100.696</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.226524</v>
+        <v>64.22653200000001</v>
       </c>
       <c r="H510" t="n">
         <v>99.84869999999999</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.489311</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H511" t="n">
         <v>100.2572</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H514" t="n">
         <v>100.5885</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H517" t="n">
         <v>100.7559</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H518" t="n">
         <v>101.2127</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H522" t="n">
         <v>101.8673</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H528" t="n">
         <v>101.4106</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.47603599999999</v>
+        <v>65.476028</v>
       </c>
       <c r="H530" t="n">
         <v>101.7912</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.926498</v>
+        <v>65.926506</v>
       </c>
       <c r="H532" t="n">
         <v>102.4915</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H533" t="n">
         <v>101.8064</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.21051</v>
+        <v>66.210503</v>
       </c>
       <c r="H534" t="n">
-        <v>102.9331</v>
+        <v>102.933</v>
       </c>
     </row>
     <row r="535">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H536" t="n">
         <v>103.0853</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.435745</v>
+        <v>66.435738</v>
       </c>
       <c r="H537" t="n">
         <v>103.2832</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H538" t="n">
         <v>103.8161</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H539" t="n">
         <v>103.7095</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H540" t="n">
         <v>103.5116</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H541" t="n">
         <v>103.8161</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H548" t="n">
         <v>103.7552</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H549" t="n">
         <v>104.6534</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H550" t="n">
         <v>105.6278</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.150627</v>
+        <v>67.150642</v>
       </c>
       <c r="H552" t="n">
         <v>104.3946</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H553" t="n">
         <v>103.8313</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H554" t="n">
         <v>102.796</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H556" t="n">
         <v>103.2223</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H558" t="n">
         <v>103.3746</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H560" t="n">
         <v>104.7448</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H562" t="n">
         <v>105.1254</v>
@@ -21846,10 +21846,10 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H564" t="n">
-        <v>104.5469</v>
+        <v>104.5468</v>
       </c>
     </row>
     <row r="565">
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H565" t="n">
         <v>104.6534</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H566" t="n">
         <v>105.3233</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.659859</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H568" t="n">
         <v>105.1863</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H572" t="n">
-        <v>105.3537</v>
+        <v>105.3538</v>
       </c>
     </row>
     <row r="573">
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H573" t="n">
         <v>105.9475</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H574" t="n">
         <v>105.0036</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.765224</v>
+        <v>53.765228</v>
       </c>
       <c r="H1510" t="n">
         <v>99.96380000000001</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1511" t="n">
         <v>100.5612</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.028114</v>
+        <v>54.028111</v>
       </c>
       <c r="H1512" t="n">
         <v>100.4526</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.645649</v>
+        <v>53.645645</v>
       </c>
       <c r="H1515" t="n">
         <v>99.7415</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.999607</v>
+        <v>53.999611</v>
       </c>
       <c r="H1517" t="n">
         <v>100.3996</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.02911</v>
+        <v>54.029106</v>
       </c>
       <c r="H1522" t="n">
         <v>100.4544</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.012352</v>
+        <v>55.012348</v>
       </c>
       <c r="H1525" t="n">
         <v>102.2825</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1526" t="n">
         <v>102.8492</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1527" t="n">
         <v>103.3428</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5256</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.943523</v>
+        <v>54.943527</v>
       </c>
       <c r="H1532" t="n">
         <v>102.1546</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.25816</v>
+        <v>55.258163</v>
       </c>
       <c r="H1533" t="n">
         <v>102.7396</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.051685</v>
+        <v>55.051682</v>
       </c>
       <c r="H1534" t="n">
         <v>102.3557</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.798939</v>
+        <v>55.798946</v>
       </c>
       <c r="H1540" t="n">
         <v>103.745</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1544" t="n">
         <v>104.33</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1545" t="n">
         <v>104.2203</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.818611</v>
+        <v>55.818607</v>
       </c>
       <c r="H1546" t="n">
         <v>103.7816</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.798939</v>
+        <v>55.798946</v>
       </c>
       <c r="H1549" t="n">
         <v>103.745</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1553" t="n">
         <v>105.2989</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.133247</v>
+        <v>56.133244</v>
       </c>
       <c r="H1556" t="n">
         <v>104.3666</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1558" t="n">
         <v>101.99</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.80587</v>
+        <v>54.805866</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8986</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1562" t="n">
         <v>102.1363</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1563" t="n">
         <v>102.9955</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1564" t="n">
         <v>104.2203</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1565" t="n">
         <v>104.2934</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1567" t="n">
         <v>104.2934</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1572" t="n">
         <v>104.915</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1573" t="n">
         <v>104.8053</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1575" t="n">
         <v>105.4269</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1577" t="n">
         <v>105.6563</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1579" t="n">
         <v>105.0877</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1581" t="n">
         <v>106.5735</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1582" t="n">
         <v>106.3717</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1587" t="n">
         <v>109.2516</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1591" t="n">
         <v>110.7924</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1592" t="n">
         <v>110.9758</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1594" t="n">
         <v>111.0125</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1598" t="n">
         <v>109.38</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1603" t="n">
         <v>111.306</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1612" t="n">
         <v>112.9019</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1613" t="n">
         <v>112.8285</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1621" t="n">
         <v>114.8646</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1623" t="n">
         <v>114.5161</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1628" t="n">
         <v>110.0587</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1629" t="n">
         <v>111.4711</v>
@@ -62506,7 +62506,7 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1634" t="n">
         <v>109.7102</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1635" t="n">
         <v>109.0682</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1636" t="n">
         <v>108.4628</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.411438</v>
+        <v>64.41145299999999</v>
       </c>
       <c r="H506" t="n">
         <v>100.1362</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.22653200000001</v>
+        <v>64.226524</v>
       </c>
       <c r="H510" t="n">
         <v>99.84869999999999</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H511" t="n">
         <v>100.2572</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H513" t="n">
         <v>100.695</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H514" t="n">
         <v>100.5885</v>
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>64.810097</v>
+        <v>64.810112</v>
       </c>
       <c r="H517" t="n">
-        <v>100.7559</v>
+        <v>100.756</v>
       </c>
     </row>
     <row r="518">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.02555099999999</v>
+        <v>65.025558</v>
       </c>
       <c r="H520" t="n">
         <v>101.0909</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H522" t="n">
         <v>101.8673</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H528" t="n">
         <v>101.4106</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.435738</v>
+        <v>66.435745</v>
       </c>
       <c r="H537" t="n">
         <v>103.2832</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H539" t="n">
         <v>103.7095</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H548" t="n">
         <v>103.7552</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H549" t="n">
         <v>104.6534</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.150642</v>
+        <v>67.15063499999999</v>
       </c>
       <c r="H552" t="n">
         <v>104.3946</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H554" t="n">
         <v>102.796</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H557" t="n">
         <v>103.0092</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H562" t="n">
         <v>105.1254</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H565" t="n">
         <v>104.6534</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H567" t="n">
         <v>105.5517</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659874</v>
       </c>
       <c r="H568" t="n">
         <v>105.1863</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.669662</v>
+        <v>67.66965500000001</v>
       </c>
       <c r="H569" t="n">
         <v>105.2015</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H570" t="n">
         <v>105.0949</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H572" t="n">
-        <v>105.3538</v>
+        <v>105.3537</v>
       </c>
     </row>
     <row r="573">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H574" t="n">
         <v>105.0036</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H575" t="n">
         <v>105.1102</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H576" t="n">
         <v>105.7107</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H577" t="n">
         <v>106.1395</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H582" t="n">
         <v>107.1194</v>
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H583" t="n">
-        <v>108.2524</v>
+        <v>108.2525</v>
       </c>
     </row>
     <row r="584">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H589" t="n">
         <v>109.8602</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H592" t="n">
         <v>111.4526</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H594" t="n">
         <v>109.5386</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H599" t="n">
         <v>110.0745</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H603" t="n">
         <v>112.065</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H605" t="n">
         <v>113.933</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H606" t="n">
         <v>113.1062</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H608" t="n">
         <v>114.6067</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H610" t="n">
         <v>115.8776</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H612" t="n">
         <v>115.4182</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H613" t="n">
         <v>115.5101</v>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H621" t="n">
-        <v>117.6844</v>
+        <v>117.6843</v>
       </c>
     </row>
     <row r="622">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H624" t="n">
         <v>114.6833</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H629" t="n">
         <v>113.688</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H630" t="n">
         <v>113.244</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.784698</v>
+        <v>53.784695</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.086533</v>
+        <v>54.086529</v>
       </c>
       <c r="H1511" t="n">
         <v>100.5612</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.284752</v>
+        <v>54.284748</v>
       </c>
       <c r="H1513" t="n">
         <v>100.9297</v>
@@ -58025,7 +58025,7 @@
         <v>54.068439</v>
       </c>
       <c r="H1516" t="n">
-        <v>100.5275</v>
+        <v>100.5276</v>
       </c>
     </row>
     <row r="1517">
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.999611</v>
+        <v>53.999607</v>
       </c>
       <c r="H1517" t="n">
         <v>100.3996</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1521" t="n">
         <v>99.6135</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.029106</v>
+        <v>54.02911</v>
       </c>
       <c r="H1522" t="n">
         <v>100.4544</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.012348</v>
+        <v>55.012352</v>
       </c>
       <c r="H1525" t="n">
         <v>102.2825</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1526" t="n">
         <v>102.8492</v>
@@ -58595,7 +58595,7 @@
         <v>55.680958</v>
       </c>
       <c r="H1531" t="n">
-        <v>103.5256</v>
+        <v>103.5257</v>
       </c>
     </row>
     <row r="1532">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.943527</v>
+        <v>54.943523</v>
       </c>
       <c r="H1532" t="n">
         <v>102.1546</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.258163</v>
+        <v>55.25816</v>
       </c>
       <c r="H1533" t="n">
         <v>102.7396</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1536" t="n">
         <v>103.7085</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1538" t="n">
         <v>103.7085</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1540" t="n">
         <v>103.745</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.113583</v>
+        <v>56.113579</v>
       </c>
       <c r="H1544" t="n">
         <v>104.33</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.054581</v>
+        <v>56.054585</v>
       </c>
       <c r="H1545" t="n">
         <v>104.2203</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1548" t="n">
         <v>103.5439</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1549" t="n">
         <v>103.745</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1550" t="n">
         <v>102.9772</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.907101</v>
+        <v>55.907104</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9461</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>56.634697</v>
+        <v>56.634693</v>
       </c>
       <c r="H1553" t="n">
         <v>105.2989</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1554" t="n">
         <v>106.085</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.805866</v>
+        <v>54.80587</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8986</v>
@@ -59694,10 +59694,10 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1560" t="n">
-        <v>102.2642</v>
+        <v>102.2643</v>
       </c>
     </row>
     <row r="1561">
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.864864</v>
+        <v>54.864861</v>
       </c>
       <c r="H1561" t="n">
         <v>102.0083</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1562" t="n">
         <v>102.1363</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1563" t="n">
         <v>102.9955</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.054581</v>
+        <v>56.054585</v>
       </c>
       <c r="H1564" t="n">
         <v>104.2203</v>
@@ -59884,10 +59884,10 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1565" t="n">
-        <v>104.2934</v>
+        <v>104.2935</v>
       </c>
     </row>
     <row r="1566">
@@ -59960,10 +59960,10 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1567" t="n">
-        <v>104.2934</v>
+        <v>104.2935</v>
       </c>
     </row>
     <row r="1568">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.516705</v>
+        <v>56.516708</v>
       </c>
       <c r="H1571" t="n">
         <v>105.0795</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.428219</v>
+        <v>56.428215</v>
       </c>
       <c r="H1572" t="n">
         <v>104.915</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.369225</v>
+        <v>56.369221</v>
       </c>
       <c r="H1573" t="n">
         <v>104.8053</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.826942</v>
+        <v>56.826939</v>
       </c>
       <c r="H1577" t="n">
         <v>105.6563</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>56.521107</v>
+        <v>56.521103</v>
       </c>
       <c r="H1579" t="n">
         <v>105.0877</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>57.320229</v>
+        <v>57.320232</v>
       </c>
       <c r="H1581" t="n">
         <v>106.5735</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>57.211708</v>
+        <v>57.211712</v>
       </c>
       <c r="H1582" t="n">
         <v>106.3717</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.760635</v>
+        <v>58.760639</v>
       </c>
       <c r="H1587" t="n">
         <v>109.2516</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>59.589363</v>
+        <v>59.589367</v>
       </c>
       <c r="H1591" t="n">
         <v>110.7924</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.688023</v>
+        <v>59.688019</v>
       </c>
       <c r="H1592" t="n">
         <v>110.9758</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.707752</v>
+        <v>59.707756</v>
       </c>
       <c r="H1594" t="n">
         <v>111.0125</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>58.8297</v>
+        <v>58.829697</v>
       </c>
       <c r="H1598" t="n">
         <v>109.38</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.865608</v>
+        <v>59.865604</v>
       </c>
       <c r="H1603" t="n">
         <v>111.306</v>
@@ -61369,7 +61369,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1604" t="n">
-        <v>110.4255</v>
+        <v>110.4256</v>
       </c>
     </row>
     <row r="1605">
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.72393</v>
+        <v>60.723927</v>
       </c>
       <c r="H1612" t="n">
         <v>112.9019</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.684464</v>
+        <v>60.684467</v>
       </c>
       <c r="H1613" t="n">
         <v>112.8285</v>
@@ -61901,7 +61901,7 @@
         <v>60.832455</v>
       </c>
       <c r="H1618" t="n">
-        <v>113.1036</v>
+        <v>113.1037</v>
       </c>
     </row>
     <row r="1619">
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.779568</v>
+        <v>61.779564</v>
       </c>
       <c r="H1621" t="n">
         <v>114.8646</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>61.592121</v>
+        <v>61.592117</v>
       </c>
       <c r="H1623" t="n">
         <v>114.5161</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>59.194729</v>
+        <v>59.194733</v>
       </c>
       <c r="H1628" t="n">
         <v>110.0587</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.954395</v>
+        <v>59.954399</v>
       </c>
       <c r="H1629" t="n">
         <v>111.4711</v>
@@ -62506,7 +62506,7 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>59.007286</v>
+        <v>59.007282</v>
       </c>
       <c r="H1634" t="n">
         <v>109.7102</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>58.66198</v>
+        <v>58.661976</v>
       </c>
       <c r="H1635" t="n">
         <v>109.0682</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>58.336407</v>
+        <v>58.336411</v>
       </c>
       <c r="H1636" t="n">
         <v>108.4628</v>
@@ -63383,7 +63383,7 @@
         <v>60.722897</v>
       </c>
       <c r="H1657" t="n">
-        <v>112.8999</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="1658">
@@ -63535,7 +63535,7 @@
         <v>60.64378</v>
       </c>
       <c r="H1661" t="n">
-        <v>112.7528</v>
+        <v>112.7529</v>
       </c>
     </row>
     <row r="1662">
@@ -63573,7 +63573,7 @@
         <v>60.485542</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.4586</v>
+        <v>112.4587</v>
       </c>
     </row>
     <row r="1663">
@@ -63839,7 +63839,7 @@
         <v>59.684475</v>
       </c>
       <c r="H1669" t="n">
-        <v>110.9692</v>
+        <v>110.9693</v>
       </c>
     </row>
     <row r="1670">
@@ -65321,7 +65321,7 @@
         <v>63.330002</v>
       </c>
       <c r="H1708" t="n">
-        <v>117.7472</v>
+        <v>117.7473</v>
       </c>
     </row>
     <row r="1709">
@@ -65435,7 +65435,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1711" t="n">
-        <v>118.5095</v>
+        <v>118.5096</v>
       </c>
     </row>
     <row r="1712">
@@ -65929,7 +65929,7 @@
         <v>63.740002</v>
       </c>
       <c r="H1724" t="n">
-        <v>118.5095</v>
+        <v>118.5096</v>
       </c>
     </row>
     <row r="1725">
@@ -66689,7 +66689,7 @@
         <v>65.629997</v>
       </c>
       <c r="H1744" t="n">
-        <v>122.0235</v>
+        <v>122.0236</v>
       </c>
     </row>
     <row r="1745">
@@ -66955,7 +66955,7 @@
         <v>65.629997</v>
       </c>
       <c r="H1751" t="n">
-        <v>122.0235</v>
+        <v>122.0236</v>
       </c>
     </row>
     <row r="1752">
@@ -67031,7 +67031,7 @@
         <v>65.510002</v>
       </c>
       <c r="H1753" t="n">
-        <v>121.8004</v>
+        <v>121.8005</v>
       </c>
     </row>
     <row r="1754">
@@ -67297,7 +67297,7 @@
         <v>64.010002</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.0115</v>
+        <v>119.0116</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>32.939999</v>
+        <v>33.09</v>
       </c>
       <c r="H253" t="n">
-        <v>109.7451</v>
+        <v>110.2449</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.865002</v>
+        <v>47.360001</v>
       </c>
       <c r="H504" t="n">
-        <v>132.9953</v>
+        <v>131.5921</v>
       </c>
     </row>
     <row r="505">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.050003</v>
+        <v>80.66999800000001</v>
       </c>
       <c r="H755" t="n">
-        <v>125.8317</v>
+        <v>125.2417</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>125.940002</v>
+        <v>125.25</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.0472</v>
+        <v>118.3949</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>125.940002</v>
+        <v>125.25</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.0472</v>
+        <v>118.3949</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>125.940002</v>
+        <v>125.25</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.0472</v>
+        <v>118.3949</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.765224</v>
+        <v>53.765228</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.028114</v>
+        <v>54.028111</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.489</v>
+        <v>100.4889</v>
       </c>
     </row>
     <row r="1512">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.068436</v>
+        <v>54.068443</v>
       </c>
       <c r="H1515" t="n">
         <v>100.564</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.999607</v>
+        <v>53.999611</v>
       </c>
       <c r="H1516" t="n">
         <v>100.4359</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.048775</v>
+        <v>54.048771</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5274</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1520" t="n">
         <v>99.64960000000001</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.127434</v>
+        <v>54.12743</v>
       </c>
       <c r="H1522" t="n">
         <v>100.6737</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.012352</v>
+        <v>55.012348</v>
       </c>
       <c r="H1524" t="n">
         <v>102.3196</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1525" t="n">
         <v>102.8865</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.562962</v>
+        <v>55.562965</v>
       </c>
       <c r="H1527" t="n">
         <v>103.3437</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1530" t="n">
         <v>103.5631</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.25816</v>
+        <v>55.258163</v>
       </c>
       <c r="H1532" t="n">
         <v>102.7768</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.051678</v>
+        <v>55.051682</v>
       </c>
       <c r="H1533" t="n">
         <v>102.3927</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.336819</v>
+        <v>55.336815</v>
       </c>
       <c r="H1534" t="n">
         <v>102.9231</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1535" t="n">
         <v>103.746</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.199162</v>
+        <v>55.199165</v>
       </c>
       <c r="H1536" t="n">
         <v>102.667</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1537" t="n">
         <v>103.746</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1539" t="n">
         <v>103.7826</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1541" t="n">
         <v>104.6787</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1542" t="n">
         <v>104.4592</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1544" t="n">
         <v>104.2581</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.848106</v>
+        <v>55.848103</v>
       </c>
       <c r="H1546" t="n">
         <v>103.874</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1547" t="n">
         <v>103.5814</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1548" t="n">
         <v>103.7826</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1549" t="n">
         <v>103.0145</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1553" t="n">
         <v>106.1234</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.828438</v>
+        <v>55.828442</v>
       </c>
       <c r="H1556" t="n">
         <v>103.8374</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1559" t="n">
         <v>102.3013</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1561" t="n">
         <v>102.1733</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1562" t="n">
         <v>103.0328</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1563" t="n">
         <v>104.2581</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6787</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1567" t="n">
         <v>104.4592</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1570" t="n">
         <v>105.1176</v>
@@ -60226,10 +60226,10 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1574" t="n">
-        <v>105.4651</v>
+        <v>105.465</v>
       </c>
     </row>
     <row r="1575">
@@ -60419,7 +60419,7 @@
         <v>57.093319</v>
       </c>
       <c r="H1579" t="n">
-        <v>106.1901</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="1580">
@@ -60685,7 +60685,7 @@
         <v>58.760635</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.2912</v>
+        <v>109.2911</v>
       </c>
     </row>
     <row r="1587">
@@ -61673,7 +61673,7 @@
         <v>60.684464</v>
       </c>
       <c r="H1612" t="n">
-        <v>112.8694</v>
+        <v>112.8693</v>
       </c>
     </row>
     <row r="1613">
@@ -62205,7 +62205,7 @@
         <v>61.019901</v>
       </c>
       <c r="H1626" t="n">
-        <v>113.4933</v>
+        <v>113.4932</v>
       </c>
     </row>
     <row r="1627">
@@ -62699,7 +62699,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1639" t="n">
-        <v>106.1718</v>
+        <v>106.1717</v>
       </c>
     </row>
     <row r="1640">
@@ -63383,7 +63383,7 @@
         <v>60.693226</v>
       </c>
       <c r="H1657" t="n">
-        <v>112.8857</v>
+        <v>112.8856</v>
       </c>
     </row>
     <row r="1658">
@@ -63573,7 +63573,7 @@
         <v>60.515209</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.5546</v>
+        <v>112.5545</v>
       </c>
     </row>
     <row r="1663">
@@ -63991,7 +63991,7 @@
         <v>60.703117</v>
       </c>
       <c r="H1673" t="n">
-        <v>112.9041</v>
+        <v>112.904</v>
       </c>
     </row>
     <row r="1674">
@@ -64447,7 +64447,7 @@
         <v>62.433819</v>
       </c>
       <c r="H1685" t="n">
-        <v>116.1231</v>
+        <v>116.123</v>
       </c>
     </row>
     <row r="1686">
@@ -64561,7 +64561,7 @@
         <v>61.899773</v>
       </c>
       <c r="H1688" t="n">
-        <v>115.1298</v>
+        <v>115.1297</v>
       </c>
     </row>
     <row r="1689">
@@ -65359,7 +65359,7 @@
         <v>63.939999</v>
       </c>
       <c r="H1709" t="n">
-        <v>118.9245</v>
+        <v>118.9244</v>
       </c>
     </row>
     <row r="1710">
@@ -65625,7 +65625,7 @@
         <v>63.919998</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.8873</v>
+        <v>118.8872</v>
       </c>
     </row>
     <row r="1717">
@@ -65663,7 +65663,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1717" t="n">
-        <v>119.0175</v>
+        <v>119.0174</v>
       </c>
     </row>
     <row r="1718">
@@ -65701,7 +65701,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1718" t="n">
-        <v>119.0175</v>
+        <v>119.0174</v>
       </c>
     </row>
     <row r="1719">
@@ -65739,7 +65739,7 @@
         <v>63.970001</v>
       </c>
       <c r="H1719" t="n">
-        <v>118.9803</v>
+        <v>118.9802</v>
       </c>
     </row>
     <row r="1720">
@@ -65853,7 +65853,7 @@
         <v>63.959999</v>
       </c>
       <c r="H1722" t="n">
-        <v>118.9617</v>
+        <v>118.9616</v>
       </c>
     </row>
     <row r="1723">
@@ -66309,7 +66309,7 @@
         <v>65.56999999999999</v>
       </c>
       <c r="H1734" t="n">
-        <v>121.9562</v>
+        <v>121.9561</v>
       </c>
     </row>
     <row r="1735">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.779999</v>
+        <v>63.5</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.6269</v>
+        <v>118.1061</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>33.09</v>
+        <v>33.174999</v>
       </c>
       <c r="H253" t="n">
-        <v>110.2449</v>
+        <v>110.5281</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.360001</v>
+        <v>47.514999</v>
       </c>
       <c r="H504" t="n">
-        <v>131.5921</v>
+        <v>132.0228</v>
       </c>
     </row>
     <row r="505">
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.859161</v>
+        <v>64.859154</v>
       </c>
       <c r="H507" t="n">
         <v>100.6951</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H508" t="n">
         <v>100.5591</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.226517</v>
+        <v>64.226524</v>
       </c>
       <c r="H509" t="n">
         <v>99.7129</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.489304</v>
+        <v>64.489311</v>
       </c>
       <c r="H510" t="n">
         <v>100.1209</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H513" t="n">
         <v>100.4517</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H516" t="n">
         <v>100.6189</v>
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H517" t="n">
-        <v>101.075</v>
+        <v>101.0751</v>
       </c>
     </row>
     <row r="518">
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H521" t="n">
         <v>101.7288</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H527" t="n">
         <v>101.2727</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.6528</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H531" t="n">
-        <v>102.3522</v>
+        <v>102.3521</v>
       </c>
     </row>
     <row r="532">
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H533" t="n">
         <v>102.7931</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H547" t="n">
         <v>103.6141</v>
@@ -21276,10 +21276,10 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H549" t="n">
-        <v>105.4842</v>
+        <v>105.4841</v>
       </c>
     </row>
     <row r="550">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H551" t="n">
         <v>104.2526</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H553" t="n">
         <v>102.6562</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H555" t="n">
-        <v>103.0819</v>
+        <v>103.082</v>
       </c>
     </row>
     <row r="556">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H558" t="n">
         <v>103.6445</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H565" t="n">
         <v>105.1801</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H566" t="n">
         <v>105.4081</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H573" t="n">
         <v>104.8608</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.66999800000001</v>
+        <v>80.639999</v>
       </c>
       <c r="H755" t="n">
-        <v>125.2417</v>
+        <v>125.1951</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>125.25</v>
+        <v>125.419998</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.3949</v>
+        <v>118.5556</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>125.25</v>
+        <v>125.419998</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.3949</v>
+        <v>118.5556</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>125.25</v>
+        <v>125.419998</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.3949</v>
+        <v>118.5556</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1510" t="n">
         <v>100.5976</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.068443</v>
+        <v>54.068439</v>
       </c>
       <c r="H1515" t="n">
         <v>100.564</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.048771</v>
+        <v>54.048775</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5274</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1520" t="n">
         <v>99.64960000000001</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.02911</v>
+        <v>54.029106</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4908</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1525" t="n">
         <v>102.8865</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1526" t="n">
-        <v>103.3803</v>
+        <v>103.3802</v>
       </c>
     </row>
     <row r="1527">
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.943523</v>
+        <v>54.943527</v>
       </c>
       <c r="H1531" t="n">
         <v>102.1916</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.336815</v>
+        <v>55.336819</v>
       </c>
       <c r="H1534" t="n">
         <v>102.9231</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1539" t="n">
         <v>103.7826</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1541" t="n">
         <v>104.6787</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1542" t="n">
         <v>104.4592</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.848103</v>
+        <v>55.848106</v>
       </c>
       <c r="H1546" t="n">
         <v>103.874</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1547" t="n">
         <v>103.5814</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1548" t="n">
         <v>103.7826</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1549" t="n">
         <v>103.0145</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1553" t="n">
         <v>106.1234</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.828442</v>
+        <v>55.828438</v>
       </c>
       <c r="H1556" t="n">
         <v>103.8374</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1557" t="n">
         <v>102.027</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.80587</v>
+        <v>54.805866</v>
       </c>
       <c r="H1558" t="n">
         <v>101.9355</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1559" t="n">
         <v>102.3013</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1561" t="n">
         <v>102.1733</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1562" t="n">
         <v>103.0328</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6787</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1567" t="n">
         <v>104.4592</v>
@@ -60226,10 +60226,10 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1574" t="n">
-        <v>105.465</v>
+        <v>105.4651</v>
       </c>
     </row>
     <row r="1575">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.5</v>
+        <v>63.490002</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.1061</v>
+        <v>118.0875</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.411446</v>
+        <v>64.41145299999999</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.975945</v>
+        <v>64.97595200000001</v>
       </c>
       <c r="H506" t="n">
         <v>100.8764</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.859154</v>
+        <v>64.859161</v>
       </c>
       <c r="H507" t="n">
         <v>100.6951</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.77156100000001</v>
+        <v>64.771568</v>
       </c>
       <c r="H508" t="n">
         <v>100.5591</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.489311</v>
+        <v>64.489304</v>
       </c>
       <c r="H510" t="n">
         <v>100.1209</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H513" t="n">
         <v>100.4517</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H516" t="n">
         <v>100.6189</v>
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H517" t="n">
-        <v>101.0751</v>
+        <v>101.075</v>
       </c>
     </row>
     <row r="518">
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H521" t="n">
         <v>101.7288</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H527" t="n">
         <v>101.2727</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.47603599999999</v>
+        <v>65.476028</v>
       </c>
       <c r="H529" t="n">
         <v>101.6528</v>
@@ -20557,7 +20557,7 @@
         <v>65.906921</v>
       </c>
       <c r="H530" t="n">
-        <v>102.3218</v>
+        <v>102.3217</v>
       </c>
     </row>
     <row r="531">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>65.926498</v>
+        <v>65.926506</v>
       </c>
       <c r="H531" t="n">
         <v>102.3521</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.21051</v>
+        <v>66.210503</v>
       </c>
       <c r="H533" t="n">
         <v>102.7931</v>
@@ -21013,7 +21013,7 @@
         <v>66.425949</v>
       </c>
       <c r="H542" t="n">
-        <v>103.1276</v>
+        <v>103.1275</v>
       </c>
     </row>
     <row r="543">
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H547" t="n">
         <v>103.6141</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H549" t="n">
         <v>105.4841</v>
@@ -21317,7 +21317,7 @@
         <v>67.434631</v>
       </c>
       <c r="H550" t="n">
-        <v>104.6936</v>
+        <v>104.6935</v>
       </c>
     </row>
     <row r="551">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.150627</v>
+        <v>67.15063499999999</v>
       </c>
       <c r="H551" t="n">
         <v>104.2526</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H553" t="n">
         <v>102.6562</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H555" t="n">
-        <v>103.082</v>
+        <v>103.0819</v>
       </c>
     </row>
     <row r="556">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H558" t="n">
         <v>103.6445</v>
@@ -21773,7 +21773,7 @@
         <v>67.434631</v>
       </c>
       <c r="H562" t="n">
-        <v>104.6936</v>
+        <v>104.6935</v>
       </c>
     </row>
     <row r="563">
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H565" t="n">
         <v>105.1801</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H566" t="n">
         <v>105.4081</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H573" t="n">
         <v>104.8608</v>
@@ -22381,7 +22381,7 @@
         <v>68.35178399999999</v>
       </c>
       <c r="H578" t="n">
-        <v>106.1175</v>
+        <v>106.1174</v>
       </c>
     </row>
     <row r="579">
@@ -22723,7 +22723,7 @@
         <v>70.577652</v>
       </c>
       <c r="H587" t="n">
-        <v>109.5732</v>
+        <v>109.5731</v>
       </c>
     </row>
     <row r="588">
@@ -22951,7 +22951,7 @@
         <v>70.459457</v>
       </c>
       <c r="H593" t="n">
-        <v>109.3897</v>
+        <v>109.3896</v>
       </c>
     </row>
     <row r="594">
@@ -23331,7 +23331,7 @@
         <v>72.78381299999999</v>
       </c>
       <c r="H603" t="n">
-        <v>112.9983</v>
+        <v>112.9982</v>
       </c>
     </row>
     <row r="604">
@@ -24167,7 +24167,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H625" t="n">
-        <v>114.1451</v>
+        <v>114.145</v>
       </c>
     </row>
     <row r="626">
@@ -24433,7 +24433,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H632" t="n">
-        <v>114.1451</v>
+        <v>114.145</v>
       </c>
     </row>
     <row r="633">
@@ -24661,7 +24661,7 @@
         <v>72.557343</v>
       </c>
       <c r="H638" t="n">
-        <v>112.6467</v>
+        <v>112.6466</v>
       </c>
     </row>
     <row r="639">
@@ -25041,7 +25041,7 @@
         <v>74.19062</v>
       </c>
       <c r="H648" t="n">
-        <v>115.1824</v>
+        <v>115.1823</v>
       </c>
     </row>
     <row r="649">
@@ -25269,7 +25269,7 @@
         <v>74.74494900000001</v>
       </c>
       <c r="H654" t="n">
-        <v>116.043</v>
+        <v>116.0429</v>
       </c>
     </row>
     <row r="655">
@@ -25459,7 +25459,7 @@
         <v>73.943153</v>
       </c>
       <c r="H659" t="n">
-        <v>114.7982</v>
+        <v>114.7981</v>
       </c>
     </row>
     <row r="660">
@@ -25915,7 +25915,7 @@
         <v>76.041679</v>
       </c>
       <c r="H671" t="n">
-        <v>118.0562</v>
+        <v>118.0561</v>
       </c>
     </row>
     <row r="672">
@@ -25991,7 +25991,7 @@
         <v>75.517044</v>
       </c>
       <c r="H673" t="n">
-        <v>117.2417</v>
+        <v>117.2416</v>
       </c>
     </row>
     <row r="674">
@@ -26599,7 +26599,7 @@
         <v>76.56630699999999</v>
       </c>
       <c r="H689" t="n">
-        <v>118.8707</v>
+        <v>118.8706</v>
       </c>
     </row>
     <row r="690">
@@ -26675,7 +26675,7 @@
         <v>77.15033</v>
       </c>
       <c r="H691" t="n">
-        <v>119.7774</v>
+        <v>119.7773</v>
       </c>
     </row>
     <row r="692">
@@ -26865,7 +26865,7 @@
         <v>78.58000199999999</v>
       </c>
       <c r="H696" t="n">
-        <v>121.997</v>
+        <v>121.9969</v>
       </c>
     </row>
     <row r="697">
@@ -26941,7 +26941,7 @@
         <v>78.980003</v>
       </c>
       <c r="H698" t="n">
-        <v>122.618</v>
+        <v>122.6179</v>
       </c>
     </row>
     <row r="699">
@@ -26979,7 +26979,7 @@
         <v>78.620003</v>
       </c>
       <c r="H699" t="n">
-        <v>122.0591</v>
+        <v>122.059</v>
       </c>
     </row>
     <row r="700">
@@ -27093,7 +27093,7 @@
         <v>78.81999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>122.3696</v>
+        <v>122.3695</v>
       </c>
     </row>
     <row r="703">
@@ -27245,7 +27245,7 @@
         <v>79.379997</v>
       </c>
       <c r="H706" t="n">
-        <v>123.239</v>
+        <v>123.2389</v>
       </c>
     </row>
     <row r="707">
@@ -27321,7 +27321,7 @@
         <v>79.970001</v>
       </c>
       <c r="H708" t="n">
-        <v>124.155</v>
+        <v>124.1549</v>
       </c>
     </row>
     <row r="709">
@@ -27397,7 +27397,7 @@
         <v>79.339996</v>
       </c>
       <c r="H710" t="n">
-        <v>123.1769</v>
+        <v>123.1768</v>
       </c>
     </row>
     <row r="711">
@@ -27511,7 +27511,7 @@
         <v>79.970001</v>
       </c>
       <c r="H713" t="n">
-        <v>124.155</v>
+        <v>124.1549</v>
       </c>
     </row>
     <row r="714">
@@ -27739,7 +27739,7 @@
         <v>80.010002</v>
       </c>
       <c r="H719" t="n">
-        <v>124.2171</v>
+        <v>124.217</v>
       </c>
     </row>
     <row r="720">
@@ -27929,7 +27929,7 @@
         <v>81.519997</v>
       </c>
       <c r="H724" t="n">
-        <v>126.5614</v>
+        <v>126.5613</v>
       </c>
     </row>
     <row r="725">
@@ -28157,7 +28157,7 @@
         <v>81.160004</v>
       </c>
       <c r="H730" t="n">
-        <v>126.0025</v>
+        <v>126.0024</v>
       </c>
     </row>
     <row r="731">
@@ -28689,7 +28689,7 @@
         <v>81.480003</v>
       </c>
       <c r="H744" t="n">
-        <v>126.4993</v>
+        <v>126.4992</v>
       </c>
     </row>
     <row r="745">
@@ -28879,7 +28879,7 @@
         <v>81.55999799999999</v>
       </c>
       <c r="H749" t="n">
-        <v>126.6235</v>
+        <v>126.6234</v>
       </c>
     </row>
     <row r="750">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.765228</v>
+        <v>53.765224</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.086533</v>
+        <v>54.086529</v>
       </c>
       <c r="H1510" t="n">
         <v>100.5976</v>
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.028111</v>
+        <v>54.028114</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.4889</v>
+        <v>100.489</v>
       </c>
     </row>
     <row r="1512">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.068439</v>
+        <v>54.068443</v>
       </c>
       <c r="H1515" t="n">
         <v>100.564</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.048775</v>
+        <v>54.048771</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5274</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1520" t="n">
         <v>99.64960000000001</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.029106</v>
+        <v>54.02911</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4908</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1525" t="n">
         <v>102.8865</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1526" t="n">
-        <v>103.3802</v>
+        <v>103.3803</v>
       </c>
     </row>
     <row r="1527">
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.943527</v>
+        <v>54.943523</v>
       </c>
       <c r="H1531" t="n">
         <v>102.1916</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.336819</v>
+        <v>55.336815</v>
       </c>
       <c r="H1534" t="n">
         <v>102.9231</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1539" t="n">
         <v>103.7826</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1541" t="n">
         <v>104.6787</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1542" t="n">
         <v>104.4592</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.848106</v>
+        <v>55.848103</v>
       </c>
       <c r="H1546" t="n">
         <v>103.874</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1547" t="n">
         <v>103.5814</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1548" t="n">
         <v>103.7826</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1549" t="n">
         <v>103.0145</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1553" t="n">
         <v>106.1234</v>
@@ -59542,10 +59542,10 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.828438</v>
+        <v>55.828442</v>
       </c>
       <c r="H1556" t="n">
-        <v>103.8374</v>
+        <v>103.8375</v>
       </c>
     </row>
     <row r="1557">
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1557" t="n">
         <v>102.027</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.805866</v>
+        <v>54.80587</v>
       </c>
       <c r="H1558" t="n">
         <v>101.9355</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1559" t="n">
         <v>102.3013</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1561" t="n">
         <v>102.1733</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1562" t="n">
         <v>103.0328</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6787</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1567" t="n">
         <v>104.4592</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1574" t="n">
         <v>105.4651</v>
@@ -60419,7 +60419,7 @@
         <v>57.093319</v>
       </c>
       <c r="H1579" t="n">
-        <v>106.19</v>
+        <v>106.1901</v>
       </c>
     </row>
     <row r="1580">
@@ -60685,7 +60685,7 @@
         <v>58.760635</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.2911</v>
+        <v>109.2912</v>
       </c>
     </row>
     <row r="1587">
@@ -61673,7 +61673,7 @@
         <v>60.684464</v>
       </c>
       <c r="H1612" t="n">
-        <v>112.8693</v>
+        <v>112.8694</v>
       </c>
     </row>
     <row r="1613">
@@ -62205,7 +62205,7 @@
         <v>61.019901</v>
       </c>
       <c r="H1626" t="n">
-        <v>113.4932</v>
+        <v>113.4933</v>
       </c>
     </row>
     <row r="1627">
@@ -62699,7 +62699,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1639" t="n">
-        <v>106.1717</v>
+        <v>106.1718</v>
       </c>
     </row>
     <row r="1640">
@@ -63383,7 +63383,7 @@
         <v>60.693226</v>
       </c>
       <c r="H1657" t="n">
-        <v>112.8856</v>
+        <v>112.8857</v>
       </c>
     </row>
     <row r="1658">
@@ -63573,7 +63573,7 @@
         <v>60.515209</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.5545</v>
+        <v>112.5546</v>
       </c>
     </row>
     <row r="1663">
@@ -63991,7 +63991,7 @@
         <v>60.703117</v>
       </c>
       <c r="H1673" t="n">
-        <v>112.904</v>
+        <v>112.9041</v>
       </c>
     </row>
     <row r="1674">
@@ -64447,7 +64447,7 @@
         <v>62.433819</v>
       </c>
       <c r="H1685" t="n">
-        <v>116.123</v>
+        <v>116.1231</v>
       </c>
     </row>
     <row r="1686">
@@ -64561,7 +64561,7 @@
         <v>61.899773</v>
       </c>
       <c r="H1688" t="n">
-        <v>115.1297</v>
+        <v>115.1298</v>
       </c>
     </row>
     <row r="1689">
@@ -65359,7 +65359,7 @@
         <v>63.939999</v>
       </c>
       <c r="H1709" t="n">
-        <v>118.9244</v>
+        <v>118.9245</v>
       </c>
     </row>
     <row r="1710">
@@ -65625,7 +65625,7 @@
         <v>63.919998</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.8872</v>
+        <v>118.8873</v>
       </c>
     </row>
     <row r="1717">
@@ -65663,7 +65663,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1717" t="n">
-        <v>119.0174</v>
+        <v>119.0175</v>
       </c>
     </row>
     <row r="1718">
@@ -65701,7 +65701,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1718" t="n">
-        <v>119.0174</v>
+        <v>119.0175</v>
       </c>
     </row>
     <row r="1719">
@@ -65739,7 +65739,7 @@
         <v>63.970001</v>
       </c>
       <c r="H1719" t="n">
-        <v>118.9802</v>
+        <v>118.9803</v>
       </c>
     </row>
     <row r="1720">
@@ -65853,7 +65853,7 @@
         <v>63.959999</v>
       </c>
       <c r="H1722" t="n">
-        <v>118.9616</v>
+        <v>118.9617</v>
       </c>
     </row>
     <row r="1723">
@@ -66309,7 +66309,7 @@
         <v>65.56999999999999</v>
       </c>
       <c r="H1734" t="n">
-        <v>121.9561</v>
+        <v>121.9562</v>
       </c>
     </row>
     <row r="1735">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.97595200000001</v>
+        <v>64.975945</v>
       </c>
       <c r="H506" t="n">
         <v>100.8764</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H512" t="n">
         <v>100.5581</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H513" t="n">
         <v>100.4517</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.810097</v>
+        <v>64.810112</v>
       </c>
       <c r="H516" t="n">
         <v>100.6189</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.02555099999999</v>
+        <v>65.025558</v>
       </c>
       <c r="H519" t="n">
         <v>100.9534</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H521" t="n">
         <v>101.7288</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H527" t="n">
         <v>101.2727</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H532" t="n">
         <v>101.668</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H535" t="n">
         <v>102.9451</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H537" t="n">
         <v>103.6749</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H539" t="n">
         <v>103.3708</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H540" t="n">
         <v>103.6749</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H547" t="n">
         <v>103.6141</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H552" t="n">
         <v>103.6901</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H553" t="n">
         <v>102.6562</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H556" t="n">
         <v>102.8691</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H557" t="n">
         <v>103.234</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H558" t="n">
         <v>103.6445</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H559" t="n">
         <v>104.6023</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H563" t="n">
         <v>104.4047</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.659859</v>
+        <v>67.659874</v>
       </c>
       <c r="H567" t="n">
         <v>105.0432</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.669662</v>
+        <v>67.66965500000001</v>
       </c>
       <c r="H568" t="n">
         <v>105.0584</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H569" t="n">
         <v>104.952</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H572" t="n">
         <v>105.8034</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H573" t="n">
         <v>104.8608</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H574" t="n">
         <v>104.9672</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H575" t="n">
         <v>105.567</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H576" t="n">
         <v>105.9951</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H581" t="n">
         <v>106.9737</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H582" t="n">
         <v>108.1052</v>
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H588" t="n">
-        <v>109.7108</v>
+        <v>109.7107</v>
       </c>
     </row>
     <row r="589">
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H591" t="n">
         <v>111.301</v>
@@ -22948,10 +22948,10 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H593" t="n">
-        <v>109.3896</v>
+        <v>109.3897</v>
       </c>
     </row>
     <row r="594">
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H598" t="n">
         <v>109.9248</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H602" t="n">
         <v>111.9126</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H604" t="n">
         <v>113.7781</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H605" t="n">
         <v>112.9524</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H607" t="n">
         <v>114.4509</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H609" t="n">
         <v>115.72</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H611" t="n">
         <v>115.2613</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H612" t="n">
         <v>115.353</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H620" t="n">
         <v>117.5243</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H623" t="n">
         <v>114.5273</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H628" t="n">
         <v>113.5334</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H629" t="n">
         <v>113.09</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.765224</v>
+        <v>53.765228</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1510" t="n">
         <v>100.5976</v>
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.028114</v>
+        <v>54.028111</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.489</v>
+        <v>100.4889</v>
       </c>
     </row>
     <row r="1512">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.068443</v>
+        <v>54.068439</v>
       </c>
       <c r="H1515" t="n">
         <v>100.564</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.048771</v>
+        <v>54.048775</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5274</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1520" t="n">
         <v>99.64960000000001</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.02911</v>
+        <v>54.029106</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4908</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1525" t="n">
         <v>102.8865</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1526" t="n">
-        <v>103.3803</v>
+        <v>103.3802</v>
       </c>
     </row>
     <row r="1527">
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.943523</v>
+        <v>54.943527</v>
       </c>
       <c r="H1531" t="n">
         <v>102.1916</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.336815</v>
+        <v>55.336819</v>
       </c>
       <c r="H1534" t="n">
         <v>102.9231</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1539" t="n">
         <v>103.7826</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1541" t="n">
         <v>104.6787</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1542" t="n">
         <v>104.4592</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.848103</v>
+        <v>55.848106</v>
       </c>
       <c r="H1546" t="n">
         <v>103.874</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1547" t="n">
         <v>103.5814</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1548" t="n">
         <v>103.7826</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1549" t="n">
         <v>103.0145</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1553" t="n">
         <v>106.1234</v>
@@ -59542,10 +59542,10 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.828442</v>
+        <v>55.828438</v>
       </c>
       <c r="H1556" t="n">
-        <v>103.8375</v>
+        <v>103.8374</v>
       </c>
     </row>
     <row r="1557">
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1557" t="n">
         <v>102.027</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.80587</v>
+        <v>54.805866</v>
       </c>
       <c r="H1558" t="n">
         <v>101.9355</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1559" t="n">
         <v>102.3013</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1561" t="n">
         <v>102.1733</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1562" t="n">
         <v>103.0328</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.280731</v>
+        <v>56.280735</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6787</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.162739</v>
+        <v>56.162743</v>
       </c>
       <c r="H1567" t="n">
         <v>104.4592</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1574" t="n">
         <v>105.4651</v>
@@ -60419,7 +60419,7 @@
         <v>57.093319</v>
       </c>
       <c r="H1579" t="n">
-        <v>106.1901</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="1580">
@@ -60685,7 +60685,7 @@
         <v>58.760635</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.2912</v>
+        <v>109.2911</v>
       </c>
     </row>
     <row r="1587">
@@ -61673,7 +61673,7 @@
         <v>60.684464</v>
       </c>
       <c r="H1612" t="n">
-        <v>112.8694</v>
+        <v>112.8693</v>
       </c>
     </row>
     <row r="1613">
@@ -62205,7 +62205,7 @@
         <v>61.019901</v>
       </c>
       <c r="H1626" t="n">
-        <v>113.4933</v>
+        <v>113.4932</v>
       </c>
     </row>
     <row r="1627">
@@ -62699,7 +62699,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1639" t="n">
-        <v>106.1718</v>
+        <v>106.1717</v>
       </c>
     </row>
     <row r="1640">
@@ -63383,7 +63383,7 @@
         <v>60.693226</v>
       </c>
       <c r="H1657" t="n">
-        <v>112.8857</v>
+        <v>112.8856</v>
       </c>
     </row>
     <row r="1658">
@@ -63573,7 +63573,7 @@
         <v>60.515209</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.5546</v>
+        <v>112.5545</v>
       </c>
     </row>
     <row r="1663">
@@ -63991,7 +63991,7 @@
         <v>60.703117</v>
       </c>
       <c r="H1673" t="n">
-        <v>112.9041</v>
+        <v>112.904</v>
       </c>
     </row>
     <row r="1674">
@@ -64447,7 +64447,7 @@
         <v>62.433819</v>
       </c>
       <c r="H1685" t="n">
-        <v>116.1231</v>
+        <v>116.123</v>
       </c>
     </row>
     <row r="1686">
@@ -64561,7 +64561,7 @@
         <v>61.899773</v>
       </c>
       <c r="H1688" t="n">
-        <v>115.1298</v>
+        <v>115.1297</v>
       </c>
     </row>
     <row r="1689">
@@ -65359,7 +65359,7 @@
         <v>63.939999</v>
       </c>
       <c r="H1709" t="n">
-        <v>118.9245</v>
+        <v>118.9244</v>
       </c>
     </row>
     <row r="1710">
@@ -65625,7 +65625,7 @@
         <v>63.919998</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.8873</v>
+        <v>118.8872</v>
       </c>
     </row>
     <row r="1717">
@@ -65663,7 +65663,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1717" t="n">
-        <v>119.0175</v>
+        <v>119.0174</v>
       </c>
     </row>
     <row r="1718">
@@ -65701,7 +65701,7 @@
         <v>63.990002</v>
       </c>
       <c r="H1718" t="n">
-        <v>119.0175</v>
+        <v>119.0174</v>
       </c>
     </row>
     <row r="1719">
@@ -65739,7 +65739,7 @@
         <v>63.970001</v>
       </c>
       <c r="H1719" t="n">
-        <v>118.9803</v>
+        <v>118.9802</v>
       </c>
     </row>
     <row r="1720">
@@ -65853,7 +65853,7 @@
         <v>63.959999</v>
       </c>
       <c r="H1722" t="n">
-        <v>118.9617</v>
+        <v>118.9616</v>
       </c>
     </row>
     <row r="1723">
@@ -66309,7 +66309,7 @@
         <v>65.56999999999999</v>
       </c>
       <c r="H1734" t="n">
-        <v>121.9562</v>
+        <v>121.9561</v>
       </c>
     </row>
     <row r="1735">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>33.084999</v>
+        <v>33.014999</v>
       </c>
       <c r="H253" t="n">
-        <v>109.6983</v>
+        <v>109.4662</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.880001</v>
+        <v>47.84</v>
       </c>
       <c r="H504" t="n">
-        <v>132.0645</v>
+        <v>131.9542</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.975945</v>
+        <v>64.97595200000001</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H507" t="n">
-        <v>99.6855</v>
+        <v>99.6854</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.226524</v>
+        <v>64.22653200000001</v>
       </c>
       <c r="H508" t="n">
         <v>98.8466</v>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.489304</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H509" t="n">
-        <v>99.251</v>
+        <v>99.25109999999999</v>
       </c>
     </row>
     <row r="510">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H511" t="n">
         <v>99.6845</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H512" t="n">
         <v>99.57899999999999</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>64.810112</v>
+        <v>64.810097</v>
       </c>
       <c r="H515" t="n">
-        <v>99.7448</v>
+        <v>99.74469999999999</v>
       </c>
     </row>
     <row r="516">
@@ -20098,10 +20098,10 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H518" t="n">
-        <v>100.0764</v>
+        <v>100.0763</v>
       </c>
     </row>
     <row r="519">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H520" t="n">
         <v>100.845</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H526" t="n">
-        <v>100.3929</v>
+        <v>100.3928</v>
       </c>
     </row>
     <row r="527">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.435745</v>
+        <v>66.435738</v>
       </c>
       <c r="H535" t="n">
         <v>102.2467</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H537" t="n">
         <v>102.6687</v>
@@ -20861,7 +20861,7 @@
         <v>66.58264200000001</v>
       </c>
       <c r="H538" t="n">
-        <v>102.4728</v>
+        <v>102.4727</v>
       </c>
     </row>
     <row r="539">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H546" t="n">
         <v>102.7139</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H547" t="n">
         <v>103.6031</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150642</v>
       </c>
       <c r="H550" t="n">
         <v>103.3469</v>
@@ -21355,7 +21355,7 @@
         <v>66.788292</v>
       </c>
       <c r="H551" t="n">
-        <v>102.7893</v>
+        <v>102.7892</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H552" t="n">
         <v>101.7644</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H555" t="n">
         <v>101.9754</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H560" t="n">
         <v>104.0704</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H563" t="n">
         <v>103.6031</v>
@@ -21884,10 +21884,10 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H565" t="n">
-        <v>104.4924</v>
+        <v>104.4923</v>
       </c>
     </row>
     <row r="566">
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.659874</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H566" t="n">
-        <v>104.1307</v>
+        <v>104.1306</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H567" t="n">
         <v>104.1457</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H568" t="n">
         <v>104.0402</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H570" t="n">
         <v>104.2964</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H572" t="n">
         <v>103.9498</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H573" t="n">
         <v>104.0553</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H574" t="n">
         <v>104.6498</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H575" t="n">
         <v>105.0743</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H580" t="n">
         <v>106.0444</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H581" t="n">
         <v>107.166</v>
@@ -22533,7 +22533,7 @@
         <v>70.16398599999999</v>
       </c>
       <c r="H582" t="n">
-        <v>107.9846</v>
+        <v>107.9845</v>
       </c>
     </row>
     <row r="583">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H587" t="n">
         <v>108.7576</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H590" t="n">
         <v>110.334</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H592" t="n">
         <v>108.4393</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H597" t="n">
         <v>108.9698</v>
@@ -23217,7 +23217,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H600" t="n">
-        <v>109.7126</v>
+        <v>109.7125</v>
       </c>
     </row>
     <row r="601">
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H601" t="n">
         <v>110.9403</v>
@@ -23293,7 +23293,7 @@
         <v>72.78381299999999</v>
       </c>
       <c r="H602" t="n">
-        <v>112.0166</v>
+        <v>112.0165</v>
       </c>
     </row>
     <row r="603">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H603" t="n">
         <v>112.7896</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H604" t="n">
         <v>111.9711</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H606" t="n">
         <v>113.4565</v>
@@ -23483,7 +23483,7 @@
         <v>73.97554</v>
       </c>
       <c r="H607" t="n">
-        <v>113.8507</v>
+        <v>113.8506</v>
       </c>
     </row>
     <row r="608">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H608" t="n">
         <v>114.7146</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H610" t="n">
         <v>114.2599</v>
@@ -23632,10 +23632,10 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H611" t="n">
-        <v>114.3509</v>
+        <v>114.3508</v>
       </c>
     </row>
     <row r="612">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H619" t="n">
         <v>116.5033</v>
@@ -24015,7 +24015,7 @@
         <v>75.423332</v>
       </c>
       <c r="H621" t="n">
-        <v>116.0789</v>
+        <v>116.0788</v>
       </c>
     </row>
     <row r="622">
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H622" t="n">
         <v>113.5323</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H627" t="n">
         <v>112.5471</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H628" t="n">
         <v>112.1075</v>
@@ -24737,7 +24737,7 @@
         <v>72.45835099999999</v>
       </c>
       <c r="H640" t="n">
-        <v>111.5157</v>
+        <v>111.5156</v>
       </c>
     </row>
     <row r="641">
@@ -24813,7 +24813,7 @@
         <v>73.091866</v>
       </c>
       <c r="H642" t="n">
-        <v>112.4907</v>
+        <v>112.4906</v>
       </c>
     </row>
     <row r="643">
@@ -24965,7 +24965,7 @@
         <v>74.358902</v>
       </c>
       <c r="H646" t="n">
-        <v>114.4407</v>
+        <v>114.4406</v>
       </c>
     </row>
     <row r="647">
@@ -25079,7 +25079,7 @@
         <v>74.24012</v>
       </c>
       <c r="H649" t="n">
-        <v>114.2579</v>
+        <v>114.2578</v>
       </c>
     </row>
     <row r="650">
@@ -25269,7 +25269,7 @@
         <v>74.29950700000001</v>
       </c>
       <c r="H654" t="n">
-        <v>114.3493</v>
+        <v>114.3492</v>
       </c>
     </row>
     <row r="655">
@@ -25307,7 +25307,7 @@
         <v>74.24012</v>
       </c>
       <c r="H655" t="n">
-        <v>114.2579</v>
+        <v>114.2578</v>
       </c>
     </row>
     <row r="656">
@@ -25535,7 +25535,7 @@
         <v>74.843941</v>
       </c>
       <c r="H661" t="n">
-        <v>115.1872</v>
+        <v>115.1871</v>
       </c>
     </row>
     <row r="662">
@@ -25725,7 +25725,7 @@
         <v>74.873634</v>
       </c>
       <c r="H666" t="n">
-        <v>115.2329</v>
+        <v>115.2328</v>
       </c>
     </row>
     <row r="667">
@@ -26637,7 +26637,7 @@
         <v>77.15033</v>
       </c>
       <c r="H690" t="n">
-        <v>118.7368</v>
+        <v>118.7367</v>
       </c>
     </row>
     <row r="691">
@@ -26789,7 +26789,7 @@
         <v>78.79351</v>
       </c>
       <c r="H694" t="n">
-        <v>121.2657</v>
+        <v>121.2656</v>
       </c>
     </row>
     <row r="695">
@@ -27169,7 +27169,7 @@
         <v>78.889999</v>
       </c>
       <c r="H704" t="n">
-        <v>121.4142</v>
+        <v>121.4141</v>
       </c>
     </row>
     <row r="705">
@@ -27815,7 +27815,7 @@
         <v>80.970001</v>
       </c>
       <c r="H721" t="n">
-        <v>124.6154</v>
+        <v>124.6153</v>
       </c>
     </row>
     <row r="722">
@@ -27853,7 +27853,7 @@
         <v>81.16999800000001</v>
       </c>
       <c r="H722" t="n">
-        <v>124.9232</v>
+        <v>124.9231</v>
       </c>
     </row>
     <row r="723">
@@ -28537,7 +28537,7 @@
         <v>80.860001</v>
       </c>
       <c r="H740" t="n">
-        <v>124.4461</v>
+        <v>124.446</v>
       </c>
     </row>
     <row r="741">
@@ -28651,7 +28651,7 @@
         <v>81.480003</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4003</v>
+        <v>125.4002</v>
       </c>
     </row>
     <row r="744">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.199997</v>
+        <v>81.33000199999999</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9693</v>
+        <v>125.1694</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.260002</v>
+        <v>126.5</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.5874</v>
+        <v>118.8128</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.260002</v>
+        <v>126.5</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.5874</v>
+        <v>118.8128</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.260002</v>
+        <v>126.5</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.5874</v>
+        <v>118.8128</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.284752</v>
+        <v>54.284748</v>
       </c>
       <c r="H1511" t="n">
         <v>100.3665</v>
@@ -57946,10 +57946,10 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.068436</v>
+        <v>54.068439</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.9665</v>
+        <v>99.9666</v>
       </c>
     </row>
     <row r="1515">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1519" t="n">
         <v>99.05759999999999</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.127434</v>
+        <v>54.12743</v>
       </c>
       <c r="H1521" t="n">
         <v>100.0756</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1524" t="n">
         <v>102.2753</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1525" t="n">
         <v>102.7661</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.562962</v>
+        <v>55.562965</v>
       </c>
       <c r="H1526" t="n">
         <v>102.7298</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1529" t="n">
         <v>102.9479</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.051678</v>
+        <v>55.051682</v>
       </c>
       <c r="H1532" t="n">
         <v>101.7845</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.199162</v>
+        <v>55.199165</v>
       </c>
       <c r="H1535" t="n">
         <v>102.0571</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1538" t="n">
         <v>103.1661</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.113583</v>
+        <v>56.113579</v>
       </c>
       <c r="H1542" t="n">
         <v>103.7478</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1546" t="n">
         <v>102.9661</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.798946</v>
+        <v>55.798943</v>
       </c>
       <c r="H1547" t="n">
         <v>103.1661</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1548" t="n">
-        <v>102.4026</v>
+        <v>102.4025</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.907101</v>
+        <v>55.907104</v>
       </c>
       <c r="H1550" t="n">
         <v>103.366</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>56.634697</v>
+        <v>56.634693</v>
       </c>
       <c r="H1551" t="n">
         <v>104.7113</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1552" t="n">
         <v>105.493</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1556" t="n">
         <v>101.4209</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1558" t="n">
         <v>101.6936</v>
@@ -59656,10 +59656,10 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.864864</v>
+        <v>54.864861</v>
       </c>
       <c r="H1559" t="n">
-        <v>101.4391</v>
+        <v>101.439</v>
       </c>
     </row>
     <row r="1560">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1560" t="n">
         <v>101.5663</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1561" t="n">
         <v>102.4207</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1563" t="n">
         <v>103.7114</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1565" t="n">
         <v>103.7114</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.428219</v>
+        <v>56.428215</v>
       </c>
       <c r="H1570" t="n">
         <v>104.3295</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.369225</v>
+        <v>56.369221</v>
       </c>
       <c r="H1571" t="n">
-        <v>104.2205</v>
+        <v>104.2204</v>
       </c>
     </row>
     <row r="1572">
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.826942</v>
+        <v>56.826939</v>
       </c>
       <c r="H1575" t="n">
         <v>105.0667</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.521107</v>
+        <v>56.521103</v>
       </c>
       <c r="H1577" t="n">
         <v>104.5013</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>57.320229</v>
+        <v>57.320232</v>
       </c>
       <c r="H1579" t="n">
         <v>105.9788</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>57.211708</v>
+        <v>57.211712</v>
       </c>
       <c r="H1580" t="n">
         <v>105.7781</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.760635</v>
+        <v>58.760639</v>
       </c>
       <c r="H1585" t="n">
         <v>108.6419</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.589363</v>
+        <v>59.589367</v>
       </c>
       <c r="H1589" t="n">
         <v>110.1741</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.688023</v>
+        <v>59.688019</v>
       </c>
       <c r="H1590" t="n">
         <v>110.3565</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.707752</v>
+        <v>59.707756</v>
       </c>
       <c r="H1592" t="n">
         <v>110.393</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.8297</v>
+        <v>58.829697</v>
       </c>
       <c r="H1596" t="n">
         <v>108.7696</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.865608</v>
+        <v>59.865604</v>
       </c>
       <c r="H1601" t="n">
         <v>110.6849</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.72393</v>
+        <v>60.723927</v>
       </c>
       <c r="H1610" t="n">
         <v>112.2718</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.684464</v>
+        <v>60.684467</v>
       </c>
       <c r="H1611" t="n">
         <v>112.1989</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.779568</v>
+        <v>61.779564</v>
       </c>
       <c r="H1619" t="n">
         <v>114.2236</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.592121</v>
+        <v>61.592117</v>
       </c>
       <c r="H1621" t="n">
         <v>113.877</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>59.194729</v>
+        <v>59.194733</v>
       </c>
       <c r="H1626" t="n">
         <v>109.4445</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>59.954395</v>
+        <v>59.954399</v>
       </c>
       <c r="H1627" t="n">
         <v>110.849</v>
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>59.007286</v>
+        <v>59.007282</v>
       </c>
       <c r="H1632" t="n">
         <v>109.0979</v>
@@ -62468,7 +62468,7 @@
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>58.66198</v>
+        <v>58.661976</v>
       </c>
       <c r="H1633" t="n">
         <v>108.4595</v>
@@ -62506,7 +62506,7 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>58.336407</v>
+        <v>58.336411</v>
       </c>
       <c r="H1634" t="n">
         <v>107.8576</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.880001</v>
+        <v>63.810001</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.107</v>
+        <v>117.9776</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>33.014999</v>
+        <v>32.799999</v>
       </c>
       <c r="H253" t="n">
-        <v>109.4662</v>
+        <v>108.7533</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.84</v>
+        <v>48.02</v>
       </c>
       <c r="H504" t="n">
-        <v>131.9542</v>
+        <v>132.4507</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.97595200000001</v>
+        <v>64.975945</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.859161</v>
+        <v>64.859154</v>
       </c>
       <c r="H506" t="n">
         <v>99.8203</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.22653200000001</v>
+        <v>64.226524</v>
       </c>
       <c r="H508" t="n">
         <v>98.8466</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H509" t="n">
         <v>99.25109999999999</v>
@@ -19987,7 +19987,7 @@
         <v>64.810097</v>
       </c>
       <c r="H515" t="n">
-        <v>99.74469999999999</v>
+        <v>99.7448</v>
       </c>
     </row>
     <row r="516">
@@ -20861,7 +20861,7 @@
         <v>66.58264200000001</v>
       </c>
       <c r="H538" t="n">
-        <v>102.4727</v>
+        <v>102.4728</v>
       </c>
     </row>
     <row r="539">
@@ -21355,7 +21355,7 @@
         <v>66.788292</v>
       </c>
       <c r="H551" t="n">
-        <v>102.7892</v>
+        <v>102.7893</v>
       </c>
     </row>
     <row r="552">
@@ -21887,7 +21887,7 @@
         <v>67.894897</v>
       </c>
       <c r="H565" t="n">
-        <v>104.4923</v>
+        <v>104.4924</v>
       </c>
     </row>
     <row r="566">
@@ -22533,7 +22533,7 @@
         <v>70.16398599999999</v>
       </c>
       <c r="H582" t="n">
-        <v>107.9845</v>
+        <v>107.9846</v>
       </c>
     </row>
     <row r="583">
@@ -23217,7 +23217,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H600" t="n">
-        <v>109.7125</v>
+        <v>109.7126</v>
       </c>
     </row>
     <row r="601">
@@ -23255,7 +23255,7 @@
         <v>72.084541</v>
       </c>
       <c r="H601" t="n">
-        <v>110.9403</v>
+        <v>110.9404</v>
       </c>
     </row>
     <row r="602">
@@ -23293,7 +23293,7 @@
         <v>72.78381299999999</v>
       </c>
       <c r="H602" t="n">
-        <v>112.0165</v>
+        <v>112.0166</v>
       </c>
     </row>
     <row r="603">
@@ -23445,7 +23445,7 @@
         <v>73.71946699999999</v>
       </c>
       <c r="H606" t="n">
-        <v>113.4565</v>
+        <v>113.4566</v>
       </c>
     </row>
     <row r="607">
@@ -23483,7 +23483,7 @@
         <v>73.97554</v>
       </c>
       <c r="H607" t="n">
-        <v>113.8506</v>
+        <v>113.8507</v>
       </c>
     </row>
     <row r="608">
@@ -23521,7 +23521,7 @@
         <v>74.536934</v>
       </c>
       <c r="H608" t="n">
-        <v>114.7146</v>
+        <v>114.7147</v>
       </c>
     </row>
     <row r="609">
@@ -23635,7 +23635,7 @@
         <v>74.300552</v>
       </c>
       <c r="H611" t="n">
-        <v>114.3508</v>
+        <v>114.3509</v>
       </c>
     </row>
     <row r="612">
@@ -24015,7 +24015,7 @@
         <v>75.423332</v>
       </c>
       <c r="H621" t="n">
-        <v>116.0788</v>
+        <v>116.0789</v>
       </c>
     </row>
     <row r="622">
@@ -24737,7 +24737,7 @@
         <v>72.45835099999999</v>
       </c>
       <c r="H640" t="n">
-        <v>111.5156</v>
+        <v>111.5157</v>
       </c>
     </row>
     <row r="641">
@@ -24813,7 +24813,7 @@
         <v>73.091866</v>
       </c>
       <c r="H642" t="n">
-        <v>112.4906</v>
+        <v>112.4907</v>
       </c>
     </row>
     <row r="643">
@@ -24965,7 +24965,7 @@
         <v>74.358902</v>
       </c>
       <c r="H646" t="n">
-        <v>114.4406</v>
+        <v>114.4407</v>
       </c>
     </row>
     <row r="647">
@@ -25079,7 +25079,7 @@
         <v>74.24012</v>
       </c>
       <c r="H649" t="n">
-        <v>114.2578</v>
+        <v>114.2579</v>
       </c>
     </row>
     <row r="650">
@@ -25269,7 +25269,7 @@
         <v>74.29950700000001</v>
       </c>
       <c r="H654" t="n">
-        <v>114.3492</v>
+        <v>114.3493</v>
       </c>
     </row>
     <row r="655">
@@ -25307,7 +25307,7 @@
         <v>74.24012</v>
       </c>
       <c r="H655" t="n">
-        <v>114.2578</v>
+        <v>114.2579</v>
       </c>
     </row>
     <row r="656">
@@ -25535,7 +25535,7 @@
         <v>74.843941</v>
       </c>
       <c r="H661" t="n">
-        <v>115.1871</v>
+        <v>115.1872</v>
       </c>
     </row>
     <row r="662">
@@ -25725,7 +25725,7 @@
         <v>74.873634</v>
       </c>
       <c r="H666" t="n">
-        <v>115.2328</v>
+        <v>115.2329</v>
       </c>
     </row>
     <row r="667">
@@ -26637,7 +26637,7 @@
         <v>77.15033</v>
       </c>
       <c r="H690" t="n">
-        <v>118.7367</v>
+        <v>118.7368</v>
       </c>
     </row>
     <row r="691">
@@ -26789,7 +26789,7 @@
         <v>78.79351</v>
       </c>
       <c r="H694" t="n">
-        <v>121.2656</v>
+        <v>121.2657</v>
       </c>
     </row>
     <row r="695">
@@ -27169,7 +27169,7 @@
         <v>78.889999</v>
       </c>
       <c r="H704" t="n">
-        <v>121.4141</v>
+        <v>121.4142</v>
       </c>
     </row>
     <row r="705">
@@ -27815,7 +27815,7 @@
         <v>80.970001</v>
       </c>
       <c r="H721" t="n">
-        <v>124.6153</v>
+        <v>124.6154</v>
       </c>
     </row>
     <row r="722">
@@ -27853,7 +27853,7 @@
         <v>81.16999800000001</v>
       </c>
       <c r="H722" t="n">
-        <v>124.9231</v>
+        <v>124.9232</v>
       </c>
     </row>
     <row r="723">
@@ -28537,7 +28537,7 @@
         <v>80.860001</v>
       </c>
       <c r="H740" t="n">
-        <v>124.446</v>
+        <v>124.4461</v>
       </c>
     </row>
     <row r="741">
@@ -28651,7 +28651,7 @@
         <v>81.480003</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4002</v>
+        <v>125.4003</v>
       </c>
     </row>
     <row r="744">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.33000199999999</v>
+        <v>81.269997</v>
       </c>
       <c r="H755" t="n">
-        <v>125.1694</v>
+        <v>125.0771</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.5</v>
+        <v>126.639999</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.8128</v>
+        <v>118.9443</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.5</v>
+        <v>126.639999</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.8128</v>
+        <v>118.9443</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.5</v>
+        <v>126.639999</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.8128</v>
+        <v>118.9443</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.086529</v>
+        <v>54.086533</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.028114</v>
+        <v>54.028111</v>
       </c>
       <c r="H1510" t="n">
         <v>99.892</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.284748</v>
+        <v>54.284752</v>
       </c>
       <c r="H1511" t="n">
         <v>100.3665</v>
@@ -57911,7 +57911,7 @@
         <v>53.645645</v>
       </c>
       <c r="H1513" t="n">
-        <v>99.1849</v>
+        <v>99.1848</v>
       </c>
     </row>
     <row r="1514">
@@ -57949,7 +57949,7 @@
         <v>54.068439</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.9666</v>
+        <v>99.9665</v>
       </c>
     </row>
     <row r="1515">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.999607</v>
+        <v>53.999611</v>
       </c>
       <c r="H1515" t="n">
         <v>99.83929999999999</v>
@@ -58025,7 +58025,7 @@
         <v>53.881622</v>
       </c>
       <c r="H1516" t="n">
-        <v>99.6212</v>
+        <v>99.6211</v>
       </c>
     </row>
     <row r="1517">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1519" t="n">
         <v>99.05759999999999</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.02911</v>
+        <v>54.029106</v>
       </c>
       <c r="H1520" t="n">
         <v>99.8938</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.012352</v>
+        <v>55.012348</v>
       </c>
       <c r="H1523" t="n">
         <v>101.7117</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1524" t="n">
         <v>102.2753</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.943523</v>
+        <v>54.943527</v>
       </c>
       <c r="H1530" t="n">
         <v>101.5845</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.25816</v>
+        <v>55.258163</v>
       </c>
       <c r="H1531" t="n">
         <v>102.1662</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1534" t="n">
         <v>103.1297</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1536" t="n">
         <v>103.1297</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1538" t="n">
         <v>103.1661</v>
@@ -58899,7 +58899,7 @@
         <v>55.995594</v>
       </c>
       <c r="H1539" t="n">
-        <v>103.5297</v>
+        <v>103.5296</v>
       </c>
     </row>
     <row r="1540">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1542" t="n">
         <v>103.7478</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1543" t="n">
         <v>103.6387</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1546" t="n">
         <v>102.9661</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1547" t="n">
         <v>103.1661</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1548" t="n">
         <v>102.4025</v>
@@ -59279,7 +59279,7 @@
         <v>55.100842</v>
       </c>
       <c r="H1549" t="n">
-        <v>101.8754</v>
+        <v>101.8753</v>
       </c>
     </row>
     <row r="1550">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.907104</v>
+        <v>55.907101</v>
       </c>
       <c r="H1550" t="n">
         <v>103.366</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1551" t="n">
         <v>104.7113</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1552" t="n">
         <v>105.493</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.80587</v>
+        <v>54.805866</v>
       </c>
       <c r="H1557" t="n">
         <v>101.33</v>
@@ -59618,10 +59618,10 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1558" t="n">
-        <v>101.6936</v>
+        <v>101.6935</v>
       </c>
     </row>
     <row r="1559">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.864861</v>
+        <v>54.864864</v>
       </c>
       <c r="H1559" t="n">
         <v>101.439</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1560" t="n">
         <v>101.5663</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1561" t="n">
         <v>102.4207</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1562" t="n">
         <v>103.6387</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1563" t="n">
         <v>103.7114</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1565" t="n">
         <v>103.7114</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1569" t="n">
         <v>104.4931</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1570" t="n">
         <v>104.3295</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1571" t="n">
         <v>104.2204</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1575" t="n">
         <v>105.0667</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1577" t="n">
         <v>104.5013</v>
@@ -60416,10 +60416,10 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1579" t="n">
-        <v>105.9788</v>
+        <v>105.9787</v>
       </c>
     </row>
     <row r="1580">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1580" t="n">
         <v>105.7781</v>
@@ -60609,7 +60609,7 @@
         <v>58.237751</v>
       </c>
       <c r="H1584" t="n">
-        <v>107.6752</v>
+        <v>107.6751</v>
       </c>
     </row>
     <row r="1585">
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1585" t="n">
         <v>108.6419</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1589" t="n">
         <v>110.1741</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1590" t="n">
         <v>110.3565</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1592" t="n">
         <v>110.393</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1596" t="n">
         <v>108.7696</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1601" t="n">
         <v>110.6849</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1610" t="n">
         <v>112.2718</v>
@@ -61632,10 +61632,10 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1611" t="n">
-        <v>112.1989</v>
+        <v>112.1988</v>
       </c>
     </row>
     <row r="1612">
@@ -61749,7 +61749,7 @@
         <v>60.418091</v>
       </c>
       <c r="H1614" t="n">
-        <v>111.7064</v>
+        <v>111.7063</v>
       </c>
     </row>
     <row r="1615">
@@ -61863,7 +61863,7 @@
         <v>61.532921</v>
       </c>
       <c r="H1617" t="n">
-        <v>113.7676</v>
+        <v>113.7675</v>
       </c>
     </row>
     <row r="1618">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1619" t="n">
         <v>114.2236</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1621" t="n">
         <v>113.877</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1626" t="n">
         <v>109.4445</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1627" t="n">
         <v>110.849</v>
@@ -62281,7 +62281,7 @@
         <v>59.135536</v>
       </c>
       <c r="H1628" t="n">
-        <v>109.3351</v>
+        <v>109.335</v>
       </c>
     </row>
     <row r="1629">
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1632" t="n">
         <v>109.0979</v>
@@ -62468,7 +62468,7 @@
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1633" t="n">
         <v>108.4595</v>
@@ -62506,10 +62506,10 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1634" t="n">
-        <v>107.8576</v>
+        <v>107.8575</v>
       </c>
     </row>
     <row r="1635">
@@ -62699,7 +62699,7 @@
         <v>56.074726</v>
       </c>
       <c r="H1639" t="n">
-        <v>103.676</v>
+        <v>103.6759</v>
       </c>
     </row>
     <row r="1640">
@@ -62851,7 +62851,7 @@
         <v>56.935131</v>
       </c>
       <c r="H1643" t="n">
-        <v>105.2668</v>
+        <v>105.2667</v>
       </c>
     </row>
     <row r="1644">
@@ -63345,7 +63345,7 @@
         <v>60.693226</v>
       </c>
       <c r="H1656" t="n">
-        <v>112.2151</v>
+        <v>112.215</v>
       </c>
     </row>
     <row r="1657">
@@ -63801,7 +63801,7 @@
         <v>60.297638</v>
       </c>
       <c r="H1668" t="n">
-        <v>111.4837</v>
+        <v>111.4836</v>
       </c>
     </row>
     <row r="1669">
@@ -63915,7 +63915,7 @@
         <v>60.623997</v>
       </c>
       <c r="H1671" t="n">
-        <v>112.0871</v>
+        <v>112.087</v>
       </c>
     </row>
     <row r="1672">
@@ -65245,7 +65245,7 @@
         <v>63.330002</v>
       </c>
       <c r="H1706" t="n">
-        <v>117.0902</v>
+        <v>117.0901</v>
       </c>
     </row>
     <row r="1707">
@@ -65473,7 +65473,7 @@
         <v>64.860001</v>
       </c>
       <c r="H1712" t="n">
-        <v>119.919</v>
+        <v>119.9189</v>
       </c>
     </row>
     <row r="1713">
@@ -65815,7 +65815,7 @@
         <v>63.959999</v>
       </c>
       <c r="H1721" t="n">
-        <v>118.255</v>
+        <v>118.2549</v>
       </c>
     </row>
     <row r="1722">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.810001</v>
+        <v>63.860001</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.9776</v>
+        <v>118.0701</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.859154</v>
+        <v>64.859161</v>
       </c>
       <c r="H506" t="n">
         <v>99.8203</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.77156100000001</v>
+        <v>64.771568</v>
       </c>
       <c r="H507" t="n">
-        <v>99.6854</v>
+        <v>99.6855</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.226524</v>
+        <v>64.226517</v>
       </c>
       <c r="H508" t="n">
         <v>98.8466</v>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.489311</v>
+        <v>64.489304</v>
       </c>
       <c r="H509" t="n">
-        <v>99.25109999999999</v>
+        <v>99.251</v>
       </c>
     </row>
     <row r="510">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H531" t="n">
         <v>100.7847</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H534" t="n">
-        <v>102.0507</v>
+        <v>102.0508</v>
       </c>
     </row>
     <row r="535">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.435738</v>
+        <v>66.435745</v>
       </c>
       <c r="H535" t="n">
         <v>102.2467</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H536" t="n">
         <v>102.7742</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H537" t="n">
         <v>102.6687</v>
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H538" t="n">
-        <v>102.4728</v>
+        <v>102.4727</v>
       </c>
     </row>
     <row r="539">
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H539" t="n">
         <v>102.7742</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H547" t="n">
         <v>103.6031</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.150642</v>
+        <v>67.15063499999999</v>
       </c>
       <c r="H550" t="n">
         <v>103.3469</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H551" t="n">
-        <v>102.7893</v>
+        <v>102.7892</v>
       </c>
     </row>
     <row r="552">
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H556" t="n">
         <v>102.3371</v>
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H557" t="n">
-        <v>102.744</v>
+        <v>102.7441</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H558" t="n">
         <v>103.6936</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.0704</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H562" t="n">
         <v>103.4976</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H563" t="n">
         <v>103.6031</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H565" t="n">
         <v>104.4924</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H566" t="n">
         <v>104.1306</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H570" t="n">
         <v>104.2964</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H571" t="n">
         <v>104.8842</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.086533</v>
+        <v>54.086529</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.028111</v>
+        <v>54.028114</v>
       </c>
       <c r="H1510" t="n">
         <v>99.892</v>
@@ -57908,10 +57908,10 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.645645</v>
+        <v>53.645649</v>
       </c>
       <c r="H1513" t="n">
-        <v>99.1848</v>
+        <v>99.1849</v>
       </c>
     </row>
     <row r="1514">
@@ -57949,7 +57949,7 @@
         <v>54.068439</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.9665</v>
+        <v>99.9666</v>
       </c>
     </row>
     <row r="1515">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.999611</v>
+        <v>53.999607</v>
       </c>
       <c r="H1515" t="n">
         <v>99.83929999999999</v>
@@ -58025,7 +58025,7 @@
         <v>53.881622</v>
       </c>
       <c r="H1516" t="n">
-        <v>99.6211</v>
+        <v>99.6212</v>
       </c>
     </row>
     <row r="1517">
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.029106</v>
+        <v>54.02911</v>
       </c>
       <c r="H1520" t="n">
         <v>99.8938</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.012348</v>
+        <v>55.012352</v>
       </c>
       <c r="H1523" t="n">
         <v>101.7117</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1524" t="n">
         <v>102.2753</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1525" t="n">
         <v>102.7661</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.680958</v>
+        <v>55.680954</v>
       </c>
       <c r="H1529" t="n">
         <v>102.9479</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.943527</v>
+        <v>54.943523</v>
       </c>
       <c r="H1530" t="n">
         <v>101.5845</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.258163</v>
+        <v>55.25816</v>
       </c>
       <c r="H1531" t="n">
         <v>102.1662</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.051682</v>
+        <v>55.051685</v>
       </c>
       <c r="H1532" t="n">
         <v>101.7845</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.798946</v>
+        <v>55.798939</v>
       </c>
       <c r="H1538" t="n">
         <v>103.1661</v>
@@ -58899,7 +58899,7 @@
         <v>55.995594</v>
       </c>
       <c r="H1539" t="n">
-        <v>103.5296</v>
+        <v>103.5297</v>
       </c>
     </row>
     <row r="1540">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.113583</v>
+        <v>56.113579</v>
       </c>
       <c r="H1542" t="n">
         <v>103.7478</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.054581</v>
+        <v>56.054585</v>
       </c>
       <c r="H1543" t="n">
         <v>103.6387</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.818607</v>
+        <v>55.818611</v>
       </c>
       <c r="H1544" t="n">
         <v>103.2024</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.798946</v>
+        <v>55.798939</v>
       </c>
       <c r="H1547" t="n">
         <v>103.1661</v>
@@ -59241,7 +59241,7 @@
         <v>55.385986</v>
       </c>
       <c r="H1548" t="n">
-        <v>102.4025</v>
+        <v>102.4026</v>
       </c>
     </row>
     <row r="1549">
@@ -59279,7 +59279,7 @@
         <v>55.100842</v>
       </c>
       <c r="H1549" t="n">
-        <v>101.8753</v>
+        <v>101.8754</v>
       </c>
     </row>
     <row r="1550">
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>56.634697</v>
+        <v>56.634693</v>
       </c>
       <c r="H1551" t="n">
         <v>104.7113</v>
@@ -59466,10 +59466,10 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>56.133244</v>
+        <v>56.133247</v>
       </c>
       <c r="H1554" t="n">
-        <v>103.7841</v>
+        <v>103.7842</v>
       </c>
     </row>
     <row r="1555">
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1556" t="n">
         <v>101.4209</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.805866</v>
+        <v>54.80587</v>
       </c>
       <c r="H1557" t="n">
         <v>101.33</v>
@@ -59621,7 +59621,7 @@
         <v>55.002514</v>
       </c>
       <c r="H1558" t="n">
-        <v>101.6935</v>
+        <v>101.6936</v>
       </c>
     </row>
     <row r="1559">
@@ -59659,7 +59659,7 @@
         <v>54.864864</v>
       </c>
       <c r="H1559" t="n">
-        <v>101.439</v>
+        <v>101.4391</v>
       </c>
     </row>
     <row r="1560">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1560" t="n">
         <v>101.5663</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1561" t="n">
         <v>102.4207</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.054581</v>
+        <v>56.054585</v>
       </c>
       <c r="H1562" t="n">
         <v>103.6387</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1563" t="n">
         <v>103.7114</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1565" t="n">
         <v>103.7114</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.428219</v>
+        <v>56.428215</v>
       </c>
       <c r="H1570" t="n">
         <v>104.3295</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.369225</v>
+        <v>56.369221</v>
       </c>
       <c r="H1571" t="n">
         <v>104.2204</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1573" t="n">
         <v>104.8385</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.826942</v>
+        <v>56.826939</v>
       </c>
       <c r="H1575" t="n">
         <v>105.0667</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.521107</v>
+        <v>56.521103</v>
       </c>
       <c r="H1577" t="n">
         <v>104.5013</v>
@@ -60416,10 +60416,10 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>57.320229</v>
+        <v>57.320232</v>
       </c>
       <c r="H1579" t="n">
-        <v>105.9787</v>
+        <v>105.9788</v>
       </c>
     </row>
     <row r="1580">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>57.211708</v>
+        <v>57.211712</v>
       </c>
       <c r="H1580" t="n">
         <v>105.7781</v>
@@ -60609,7 +60609,7 @@
         <v>58.237751</v>
       </c>
       <c r="H1584" t="n">
-        <v>107.6751</v>
+        <v>107.6752</v>
       </c>
     </row>
     <row r="1585">
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.760635</v>
+        <v>58.760639</v>
       </c>
       <c r="H1585" t="n">
         <v>108.6419</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.589363</v>
+        <v>59.589367</v>
       </c>
       <c r="H1589" t="n">
         <v>110.1741</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.688023</v>
+        <v>59.688019</v>
       </c>
       <c r="H1590" t="n">
         <v>110.3565</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.707752</v>
+        <v>59.707756</v>
       </c>
       <c r="H1592" t="n">
         <v>110.393</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.8297</v>
+        <v>58.829697</v>
       </c>
       <c r="H1596" t="n">
         <v>108.7696</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.865608</v>
+        <v>59.865604</v>
       </c>
       <c r="H1601" t="n">
         <v>110.6849</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.72393</v>
+        <v>60.723927</v>
       </c>
       <c r="H1610" t="n">
         <v>112.2718</v>
@@ -61632,10 +61632,10 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.684464</v>
+        <v>60.684467</v>
       </c>
       <c r="H1611" t="n">
-        <v>112.1988</v>
+        <v>112.1989</v>
       </c>
     </row>
     <row r="1612">
@@ -61749,7 +61749,7 @@
         <v>60.418091</v>
       </c>
       <c r="H1614" t="n">
-        <v>111.7063</v>
+        <v>111.7064</v>
       </c>
     </row>
     <row r="1615">
@@ -61863,7 +61863,7 @@
         <v>61.532921</v>
       </c>
       <c r="H1617" t="n">
-        <v>113.7675</v>
+        <v>113.7676</v>
       </c>
     </row>
     <row r="1618">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.779568</v>
+        <v>61.779564</v>
       </c>
       <c r="H1619" t="n">
         <v>114.2236</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.592121</v>
+        <v>61.592117</v>
       </c>
       <c r="H1621" t="n">
         <v>113.877</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>59.194729</v>
+        <v>59.194733</v>
       </c>
       <c r="H1626" t="n">
         <v>109.4445</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>59.954395</v>
+        <v>59.954399</v>
       </c>
       <c r="H1627" t="n">
         <v>110.849</v>
@@ -62281,7 +62281,7 @@
         <v>59.135536</v>
       </c>
       <c r="H1628" t="n">
-        <v>109.335</v>
+        <v>109.3351</v>
       </c>
     </row>
     <row r="1629">
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>59.007286</v>
+        <v>59.007282</v>
       </c>
       <c r="H1632" t="n">
         <v>109.0979</v>
@@ -62468,7 +62468,7 @@
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>58.66198</v>
+        <v>58.661976</v>
       </c>
       <c r="H1633" t="n">
         <v>108.4595</v>
@@ -62506,10 +62506,10 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>58.336407</v>
+        <v>58.336411</v>
       </c>
       <c r="H1634" t="n">
-        <v>107.8575</v>
+        <v>107.8576</v>
       </c>
     </row>
     <row r="1635">
@@ -62699,7 +62699,7 @@
         <v>56.074726</v>
       </c>
       <c r="H1639" t="n">
-        <v>103.6759</v>
+        <v>103.676</v>
       </c>
     </row>
     <row r="1640">
@@ -62851,7 +62851,7 @@
         <v>56.935131</v>
       </c>
       <c r="H1643" t="n">
-        <v>105.2667</v>
+        <v>105.2668</v>
       </c>
     </row>
     <row r="1644">
@@ -63345,7 +63345,7 @@
         <v>60.693226</v>
       </c>
       <c r="H1656" t="n">
-        <v>112.215</v>
+        <v>112.2151</v>
       </c>
     </row>
     <row r="1657">
@@ -63801,7 +63801,7 @@
         <v>60.297638</v>
       </c>
       <c r="H1668" t="n">
-        <v>111.4836</v>
+        <v>111.4837</v>
       </c>
     </row>
     <row r="1669">
@@ -63915,7 +63915,7 @@
         <v>60.623997</v>
       </c>
       <c r="H1671" t="n">
-        <v>112.087</v>
+        <v>112.0871</v>
       </c>
     </row>
     <row r="1672">
@@ -65245,7 +65245,7 @@
         <v>63.330002</v>
       </c>
       <c r="H1706" t="n">
-        <v>117.0901</v>
+        <v>117.0902</v>
       </c>
     </row>
     <row r="1707">
@@ -65473,7 +65473,7 @@
         <v>64.860001</v>
       </c>
       <c r="H1712" t="n">
-        <v>119.9189</v>
+        <v>119.919</v>
       </c>
     </row>
     <row r="1713">
@@ -65815,7 +65815,7 @@
         <v>63.959999</v>
       </c>
       <c r="H1721" t="n">
-        <v>118.2549</v>
+        <v>118.255</v>
       </c>
     </row>
     <row r="1722">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.975945</v>
+        <v>64.97595200000001</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H507" t="n">
-        <v>99.6855</v>
+        <v>99.6854</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.226517</v>
+        <v>64.226524</v>
       </c>
       <c r="H508" t="n">
         <v>98.8466</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.489304</v>
+        <v>64.489311</v>
       </c>
       <c r="H509" t="n">
         <v>99.251</v>
@@ -19987,7 +19987,7 @@
         <v>64.810097</v>
       </c>
       <c r="H515" t="n">
-        <v>99.7448</v>
+        <v>99.74469999999999</v>
       </c>
     </row>
     <row r="516">
@@ -20709,7 +20709,7 @@
         <v>66.308441</v>
       </c>
       <c r="H534" t="n">
-        <v>102.0508</v>
+        <v>102.0507</v>
       </c>
     </row>
     <row r="535">
@@ -21583,7 +21583,7 @@
         <v>66.75891900000001</v>
       </c>
       <c r="H557" t="n">
-        <v>102.7441</v>
+        <v>102.744</v>
       </c>
     </row>
     <row r="558">
@@ -21621,7 +21621,7 @@
         <v>67.37587000000001</v>
       </c>
       <c r="H558" t="n">
-        <v>103.6936</v>
+        <v>103.6935</v>
       </c>
     </row>
     <row r="559">
@@ -21697,7 +21697,7 @@
         <v>67.62069700000001</v>
       </c>
       <c r="H560" t="n">
-        <v>104.0704</v>
+        <v>104.0703</v>
       </c>
     </row>
     <row r="561">
@@ -22533,7 +22533,7 @@
         <v>70.16398599999999</v>
       </c>
       <c r="H582" t="n">
-        <v>107.9846</v>
+        <v>107.9845</v>
       </c>
     </row>
     <row r="583">
@@ -23217,7 +23217,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H600" t="n">
-        <v>109.7126</v>
+        <v>109.7125</v>
       </c>
     </row>
     <row r="601">
@@ -23255,7 +23255,7 @@
         <v>72.084541</v>
       </c>
       <c r="H601" t="n">
-        <v>110.9404</v>
+        <v>110.9403</v>
       </c>
     </row>
     <row r="602">
@@ -23293,7 +23293,7 @@
         <v>72.78381299999999</v>
       </c>
       <c r="H602" t="n">
-        <v>112.0166</v>
+        <v>112.0165</v>
       </c>
     </row>
     <row r="603">
@@ -23445,7 +23445,7 @@
         <v>73.71946699999999</v>
       </c>
       <c r="H606" t="n">
-        <v>113.4566</v>
+        <v>113.4565</v>
       </c>
     </row>
     <row r="607">
@@ -23483,7 +23483,7 @@
         <v>73.97554</v>
       </c>
       <c r="H607" t="n">
-        <v>113.8507</v>
+        <v>113.8506</v>
       </c>
     </row>
     <row r="608">
@@ -23521,7 +23521,7 @@
         <v>74.536934</v>
       </c>
       <c r="H608" t="n">
-        <v>114.7147</v>
+        <v>114.7146</v>
       </c>
     </row>
     <row r="609">
@@ -23635,7 +23635,7 @@
         <v>74.300552</v>
       </c>
       <c r="H611" t="n">
-        <v>114.3509</v>
+        <v>114.3508</v>
       </c>
     </row>
     <row r="612">
@@ -24015,7 +24015,7 @@
         <v>75.423332</v>
       </c>
       <c r="H621" t="n">
-        <v>116.0789</v>
+        <v>116.0788</v>
       </c>
     </row>
     <row r="622">
@@ -24737,7 +24737,7 @@
         <v>72.45835099999999</v>
       </c>
       <c r="H640" t="n">
-        <v>111.5157</v>
+        <v>111.5156</v>
       </c>
     </row>
     <row r="641">
@@ -24813,7 +24813,7 @@
         <v>73.091866</v>
       </c>
       <c r="H642" t="n">
-        <v>112.4907</v>
+        <v>112.4906</v>
       </c>
     </row>
     <row r="643">
@@ -24965,7 +24965,7 @@
         <v>74.358902</v>
       </c>
       <c r="H646" t="n">
-        <v>114.4407</v>
+        <v>114.4406</v>
       </c>
     </row>
     <row r="647">
@@ -25079,7 +25079,7 @@
         <v>74.24012</v>
       </c>
       <c r="H649" t="n">
-        <v>114.2579</v>
+        <v>114.2578</v>
       </c>
     </row>
     <row r="650">
@@ -25269,7 +25269,7 @@
         <v>74.29950700000001</v>
       </c>
       <c r="H654" t="n">
-        <v>114.3493</v>
+        <v>114.3492</v>
       </c>
     </row>
     <row r="655">
@@ -25307,7 +25307,7 @@
         <v>74.24012</v>
       </c>
       <c r="H655" t="n">
-        <v>114.2579</v>
+        <v>114.2578</v>
       </c>
     </row>
     <row r="656">
@@ -25535,7 +25535,7 @@
         <v>74.843941</v>
       </c>
       <c r="H661" t="n">
-        <v>115.1872</v>
+        <v>115.1871</v>
       </c>
     </row>
     <row r="662">
@@ -25725,7 +25725,7 @@
         <v>74.873634</v>
       </c>
       <c r="H666" t="n">
-        <v>115.2329</v>
+        <v>115.2328</v>
       </c>
     </row>
     <row r="667">
@@ -26637,7 +26637,7 @@
         <v>77.15033</v>
       </c>
       <c r="H690" t="n">
-        <v>118.7368</v>
+        <v>118.7367</v>
       </c>
     </row>
     <row r="691">
@@ -26789,7 +26789,7 @@
         <v>78.79351</v>
       </c>
       <c r="H694" t="n">
-        <v>121.2657</v>
+        <v>121.2656</v>
       </c>
     </row>
     <row r="695">
@@ -27169,7 +27169,7 @@
         <v>78.889999</v>
       </c>
       <c r="H704" t="n">
-        <v>121.4142</v>
+        <v>121.4141</v>
       </c>
     </row>
     <row r="705">
@@ -27815,7 +27815,7 @@
         <v>80.970001</v>
       </c>
       <c r="H721" t="n">
-        <v>124.6154</v>
+        <v>124.6153</v>
       </c>
     </row>
     <row r="722">
@@ -27853,7 +27853,7 @@
         <v>81.16999800000001</v>
       </c>
       <c r="H722" t="n">
-        <v>124.9232</v>
+        <v>124.9231</v>
       </c>
     </row>
     <row r="723">
@@ -28537,7 +28537,7 @@
         <v>80.860001</v>
       </c>
       <c r="H740" t="n">
-        <v>124.4461</v>
+        <v>124.446</v>
       </c>
     </row>
     <row r="741">
@@ -28651,7 +28651,7 @@
         <v>81.480003</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4003</v>
+        <v>125.4002</v>
       </c>
     </row>
     <row r="744">
@@ -29107,7 +29107,7 @@
         <v>81.269997</v>
       </c>
       <c r="H755" t="n">
-        <v>125.0771</v>
+        <v>125.077</v>
       </c>
     </row>
     <row r="756">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.284752</v>
+        <v>54.284748</v>
       </c>
       <c r="H1511" t="n">
         <v>100.3665</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.645649</v>
+        <v>53.645645</v>
       </c>
       <c r="H1513" t="n">
         <v>99.1849</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1519" t="n">
         <v>99.05759999999999</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1525" t="n">
         <v>102.7661</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1529" t="n">
         <v>102.9479</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.051685</v>
+        <v>55.051682</v>
       </c>
       <c r="H1532" t="n">
         <v>101.7845</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1534" t="n">
         <v>103.1297</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1536" t="n">
         <v>103.1297</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.798939</v>
+        <v>55.798943</v>
       </c>
       <c r="H1538" t="n">
         <v>103.1661</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.818611</v>
+        <v>55.818607</v>
       </c>
       <c r="H1544" t="n">
         <v>103.2024</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1546" t="n">
         <v>102.9661</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.798939</v>
+        <v>55.798943</v>
       </c>
       <c r="H1547" t="n">
         <v>103.1661</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1548" t="n">
-        <v>102.4026</v>
+        <v>102.4025</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.907101</v>
+        <v>55.907104</v>
       </c>
       <c r="H1550" t="n">
         <v>103.366</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1552" t="n">
         <v>105.493</v>
@@ -59466,10 +59466,10 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>56.133247</v>
+        <v>56.133244</v>
       </c>
       <c r="H1554" t="n">
-        <v>103.7842</v>
+        <v>103.7841</v>
       </c>
     </row>
     <row r="1555">
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1556" t="n">
         <v>101.4209</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1558" t="n">
         <v>101.6936</v>
@@ -59656,10 +59656,10 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>54.864864</v>
+        <v>54.864861</v>
       </c>
       <c r="H1559" t="n">
-        <v>101.4391</v>
+        <v>101.439</v>
       </c>
     </row>
     <row r="1560">
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.516705</v>
+        <v>56.516708</v>
       </c>
       <c r="H1569" t="n">
         <v>104.4931</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1573" t="n">
         <v>104.8385</v>
